--- a/tests/release_reference/workbooks/yoy_reports.xlsx
+++ b/tests/release_reference/workbooks/yoy_reports.xlsx
@@ -1269,7 +1269,9 @@
         <f>IF(E35=0, "N/A", (F35-E35)/E35)</f>
         <v/>
       </c>
-      <c r="H35" s="3" t="n"/>
+      <c r="H35" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="I35" s="3" t="n">
         <v>2</v>
       </c>
@@ -1338,11 +1340,11 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Buzos</t>
+          <t>Buzos C Capucha</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C37" s="3" t="n"/>
       <c r="D37" s="6">
@@ -1350,17 +1352,19 @@
         <v/>
       </c>
       <c r="E37" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="3" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="G37" s="6">
         <f>IF(E37=0, "N/A", (F37-E37)/E37)</f>
         <v/>
       </c>
-      <c r="H37" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="I37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+      <c r="I37" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J37" s="6">
         <f>IF(H37=0, "N/A", (I37-H37)/H37)</f>
         <v/>
@@ -1381,11 +1385,11 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Capucha</t>
+          <t>Buzos C Redondo Rustico</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C38" s="3" t="n"/>
       <c r="D38" s="6">
@@ -1393,21 +1397,17 @@
         <v/>
       </c>
       <c r="E38" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F38" s="3" t="n"/>
       <c r="G38" s="6">
         <f>IF(E38=0, "N/A", (F38-E38)/E38)</f>
         <v/>
       </c>
       <c r="H38" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I38" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="I38" s="3" t="n"/>
       <c r="J38" s="6">
         <f>IF(H38=0, "N/A", (I38-H38)/H38)</f>
         <v/>
@@ -3270,7 +3270,9 @@
         <f>IF(E111=0, "N/A", (F111-E111)/E111)</f>
         <v/>
       </c>
-      <c r="H111" s="8" t="n"/>
+      <c r="H111" s="8" t="n">
+        <v>112000</v>
+      </c>
       <c r="I111" s="8" t="n">
         <v>113900</v>
       </c>
@@ -3339,11 +3341,11 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Buzos</t>
+          <t>Buzos C Capucha</t>
         </is>
       </c>
       <c r="B113" s="8" t="n">
-        <v>79800</v>
+        <v>63000</v>
       </c>
       <c r="C113" s="8" t="n"/>
       <c r="D113" s="6">
@@ -3351,17 +3353,19 @@
         <v/>
       </c>
       <c r="E113" s="8" t="n">
-        <v>39900</v>
-      </c>
-      <c r="F113" s="8" t="n"/>
+        <v>127300</v>
+      </c>
+      <c r="F113" s="8" t="n">
+        <v>194500</v>
+      </c>
       <c r="G113" s="6">
         <f>IF(E113=0, "N/A", (F113-E113)/E113)</f>
         <v/>
       </c>
-      <c r="H113" s="8" t="n">
-        <v>267000</v>
-      </c>
-      <c r="I113" s="8" t="n"/>
+      <c r="H113" s="8" t="n"/>
+      <c r="I113" s="8" t="n">
+        <v>49900</v>
+      </c>
       <c r="J113" s="6">
         <f>IF(H113=0, "N/A", (I113-H113)/H113)</f>
         <v/>
@@ -3382,11 +3386,11 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Capucha</t>
+          <t>Buzos C Redondo Rustico</t>
         </is>
       </c>
       <c r="B114" s="8" t="n">
-        <v>63000</v>
+        <v>79800</v>
       </c>
       <c r="C114" s="8" t="n"/>
       <c r="D114" s="6">
@@ -3394,21 +3398,17 @@
         <v/>
       </c>
       <c r="E114" s="8" t="n">
-        <v>127300</v>
-      </c>
-      <c r="F114" s="8" t="n">
-        <v>194500</v>
-      </c>
+        <v>39900</v>
+      </c>
+      <c r="F114" s="8" t="n"/>
       <c r="G114" s="6">
         <f>IF(E114=0, "N/A", (F114-E114)/E114)</f>
         <v/>
       </c>
       <c r="H114" s="8" t="n">
-        <v>112000</v>
-      </c>
-      <c r="I114" s="8" t="n">
-        <v>49900</v>
-      </c>
+        <v>267000</v>
+      </c>
+      <c r="I114" s="8" t="n"/>
       <c r="J114" s="6">
         <f>IF(H114=0, "N/A", (I114-H114)/H114)</f>
         <v/>
@@ -5288,7 +5288,9 @@
         <f>IF(B33=0, "N/A", (C33-B33)/B33)</f>
         <v/>
       </c>
-      <c r="E33" s="3" t="n"/>
+      <c r="E33" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="F33" s="3" t="n"/>
       <c r="G33" s="6">
         <f>IF(E33=0, "N/A", (F33-E33)/E33)</f>
@@ -5363,29 +5365,35 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Buzos</t>
+          <t>Buzos C Capucha</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C35" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="D35" s="6">
         <f>IF(B35=0, "N/A", (C35-B35)/B35)</f>
         <v/>
       </c>
       <c r="E35" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F35" s="3" t="n"/>
       <c r="G35" s="6">
         <f>IF(E35=0, "N/A", (F35-E35)/E35)</f>
         <v/>
       </c>
       <c r="H35" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I35" s="3" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>24</v>
+      </c>
       <c r="J35" s="6">
         <f>IF(H35=0, "N/A", (I35-H35)/H35)</f>
         <v/>
@@ -5406,35 +5414,29 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Capucha</t>
+          <t>Buzos C Redondo Rustico</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="3" t="n">
-        <v>5</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="C36" s="3" t="n"/>
       <c r="D36" s="6">
         <f>IF(B36=0, "N/A", (C36-B36)/B36)</f>
         <v/>
       </c>
       <c r="E36" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F36" s="3" t="n">
         <v>1</v>
       </c>
+      <c r="F36" s="3" t="n"/>
       <c r="G36" s="6">
         <f>IF(E36=0, "N/A", (F36-E36)/E36)</f>
         <v/>
       </c>
       <c r="H36" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="I36" s="3" t="n">
-        <v>24</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I36" s="3" t="n"/>
       <c r="J36" s="6">
         <f>IF(H36=0, "N/A", (I36-H36)/H36)</f>
         <v/>
@@ -7283,7 +7285,9 @@
         <f>IF(B109=0, "N/A", (C109-B109)/B109)</f>
         <v/>
       </c>
-      <c r="E109" s="8" t="n"/>
+      <c r="E109" s="8" t="n">
+        <v>47881.5866</v>
+      </c>
       <c r="F109" s="8" t="n"/>
       <c r="G109" s="6">
         <f>IF(E109=0, "N/A", (F109-E109)/E109)</f>
@@ -7358,29 +7362,35 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Buzos</t>
+          <t>Buzos C Capucha</t>
         </is>
       </c>
       <c r="B111" s="8" t="n">
-        <v>119700</v>
-      </c>
-      <c r="C111" s="8" t="n"/>
+        <v>46900</v>
+      </c>
+      <c r="C111" s="8" t="n">
+        <v>266100</v>
+      </c>
       <c r="D111" s="6">
         <f>IF(B111=0, "N/A", (C111-B111)/B111)</f>
         <v/>
       </c>
       <c r="E111" s="8" t="n">
-        <v>39999</v>
-      </c>
-      <c r="F111" s="8" t="n"/>
+        <v>191726.861</v>
+      </c>
+      <c r="F111" s="8" t="n">
+        <v>38900</v>
+      </c>
       <c r="G111" s="6">
         <f>IF(E111=0, "N/A", (F111-E111)/E111)</f>
         <v/>
       </c>
       <c r="H111" s="8" t="n">
-        <v>44500</v>
-      </c>
-      <c r="I111" s="8" t="n"/>
+        <v>814500</v>
+      </c>
+      <c r="I111" s="8" t="n">
+        <v>1311854.164</v>
+      </c>
       <c r="J111" s="6">
         <f>IF(H111=0, "N/A", (I111-H111)/H111)</f>
         <v/>
@@ -7401,35 +7411,29 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Capucha</t>
+          <t>Buzos C Redondo Rustico</t>
         </is>
       </c>
       <c r="B112" s="8" t="n">
-        <v>46900</v>
-      </c>
-      <c r="C112" s="8" t="n">
-        <v>266100</v>
-      </c>
+        <v>119700</v>
+      </c>
+      <c r="C112" s="8" t="n"/>
       <c r="D112" s="6">
         <f>IF(B112=0, "N/A", (C112-B112)/B112)</f>
         <v/>
       </c>
       <c r="E112" s="8" t="n">
-        <v>239608.4476</v>
-      </c>
-      <c r="F112" s="8" t="n">
-        <v>38900</v>
-      </c>
+        <v>39999</v>
+      </c>
+      <c r="F112" s="8" t="n"/>
       <c r="G112" s="6">
         <f>IF(E112=0, "N/A", (F112-E112)/E112)</f>
         <v/>
       </c>
       <c r="H112" s="8" t="n">
-        <v>814500</v>
-      </c>
-      <c r="I112" s="8" t="n">
-        <v>1311854.164</v>
-      </c>
+        <v>44500</v>
+      </c>
+      <c r="I112" s="8" t="n"/>
       <c r="J112" s="6">
         <f>IF(H112=0, "N/A", (I112-H112)/H112)</f>
         <v/>
@@ -9463,25 +9467,35 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Buzos</t>
+          <t>Buzos C Capucha</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" s="3" t="n"/>
+        <v>37</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>23</v>
+      </c>
       <c r="D38" s="6">
         <f>IF(B38=0, "N/A", (C38-B38)/B38)</f>
         <v/>
       </c>
-      <c r="E38" s="3" t="n"/>
-      <c r="F38" s="3" t="n"/>
+      <c r="E38" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>6</v>
+      </c>
       <c r="G38" s="6">
         <f>IF(E38=0, "N/A", (F38-E38)/E38)</f>
         <v/>
       </c>
-      <c r="H38" s="3" t="n"/>
-      <c r="I38" s="3" t="n"/>
+      <c r="H38" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>105</v>
+      </c>
       <c r="J38" s="6">
         <f>IF(H38=0, "N/A", (I38-H38)/H38)</f>
         <v/>
@@ -9502,35 +9516,25 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Capucha</t>
+          <t>Buzos C Redondo Rustico</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>23</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C39" s="3" t="n"/>
       <c r="D39" s="6">
         <f>IF(B39=0, "N/A", (C39-B39)/B39)</f>
         <v/>
       </c>
-      <c r="E39" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>6</v>
-      </c>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="n"/>
       <c r="G39" s="6">
         <f>IF(E39=0, "N/A", (F39-E39)/E39)</f>
         <v/>
       </c>
-      <c r="H39" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v>105</v>
-      </c>
+      <c r="H39" s="3" t="n"/>
+      <c r="I39" s="3" t="n"/>
       <c r="J39" s="6">
         <f>IF(H39=0, "N/A", (I39-H39)/H39)</f>
         <v/>
@@ -11646,25 +11650,35 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Buzos</t>
+          <t>Buzos C Capucha</t>
         </is>
       </c>
       <c r="B120" s="8" t="n">
-        <v>39999</v>
-      </c>
-      <c r="C120" s="8" t="n"/>
+        <v>1855652.1406</v>
+      </c>
+      <c r="C120" s="8" t="n">
+        <v>1262700</v>
+      </c>
       <c r="D120" s="6">
         <f>IF(B120=0, "N/A", (C120-B120)/B120)</f>
         <v/>
       </c>
-      <c r="E120" s="8" t="n"/>
-      <c r="F120" s="8" t="n"/>
+      <c r="E120" s="8" t="n">
+        <v>1657200.4143</v>
+      </c>
+      <c r="F120" s="8" t="n">
+        <v>358100</v>
+      </c>
       <c r="G120" s="6">
         <f>IF(E120=0, "N/A", (F120-E120)/E120)</f>
         <v/>
       </c>
-      <c r="H120" s="8" t="n"/>
-      <c r="I120" s="8" t="n"/>
+      <c r="H120" s="8" t="n">
+        <v>6779186.0905</v>
+      </c>
+      <c r="I120" s="8" t="n">
+        <v>5945676.4474</v>
+      </c>
       <c r="J120" s="6">
         <f>IF(H120=0, "N/A", (I120-H120)/H120)</f>
         <v/>
@@ -11685,35 +11699,25 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Capucha</t>
+          <t>Buzos C Redondo Rustico</t>
         </is>
       </c>
       <c r="B121" s="8" t="n">
-        <v>1855652.1406</v>
-      </c>
-      <c r="C121" s="8" t="n">
-        <v>1262700</v>
-      </c>
+        <v>39999</v>
+      </c>
+      <c r="C121" s="8" t="n"/>
       <c r="D121" s="6">
         <f>IF(B121=0, "N/A", (C121-B121)/B121)</f>
         <v/>
       </c>
-      <c r="E121" s="8" t="n">
-        <v>1657200.4143</v>
-      </c>
-      <c r="F121" s="8" t="n">
-        <v>358100</v>
-      </c>
+      <c r="E121" s="8" t="n"/>
+      <c r="F121" s="8" t="n"/>
       <c r="G121" s="6">
         <f>IF(E121=0, "N/A", (F121-E121)/E121)</f>
         <v/>
       </c>
-      <c r="H121" s="8" t="n">
-        <v>6779186.0905</v>
-      </c>
-      <c r="I121" s="8" t="n">
-        <v>5945676.4474</v>
-      </c>
+      <c r="H121" s="8" t="n"/>
+      <c r="I121" s="8" t="n"/>
       <c r="J121" s="6">
         <f>IF(H121=0, "N/A", (I121-H121)/H121)</f>
         <v/>
@@ -13791,7 +13795,9 @@
           <t>Buzo C Capucha Rustico</t>
         </is>
       </c>
-      <c r="B36" s="3" t="n"/>
+      <c r="B36" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="C36" s="3" t="n"/>
       <c r="D36" s="6">
         <f>IF(B36=0, "N/A", (C36-B36)/B36)</f>
@@ -13876,25 +13882,35 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Buzos</t>
+          <t>Buzos C Capucha</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" s="3" t="n"/>
+        <v>57</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>25</v>
+      </c>
       <c r="D38" s="6">
         <f>IF(B38=0, "N/A", (C38-B38)/B38)</f>
         <v/>
       </c>
-      <c r="E38" s="3" t="n"/>
-      <c r="F38" s="3" t="n"/>
+      <c r="E38" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>39</v>
+      </c>
       <c r="G38" s="6">
         <f>IF(E38=0, "N/A", (F38-E38)/E38)</f>
         <v/>
       </c>
-      <c r="H38" s="3" t="n"/>
-      <c r="I38" s="3" t="n"/>
+      <c r="H38" s="3" t="n">
+        <v>234</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>83</v>
+      </c>
       <c r="J38" s="6">
         <f>IF(H38=0, "N/A", (I38-H38)/H38)</f>
         <v/>
@@ -13915,34 +13931,28 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Capucha</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="n">
-        <v>58</v>
-      </c>
+          <t>Buzos C Capucha Orangutan</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n"/>
       <c r="C39" s="3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D39" s="6">
         <f>IF(B39=0, "N/A", (C39-B39)/B39)</f>
         <v/>
       </c>
-      <c r="E39" s="3" t="n">
-        <v>43</v>
-      </c>
+      <c r="E39" s="3" t="n"/>
       <c r="F39" s="3" t="n">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="G39" s="6">
         <f>IF(E39=0, "N/A", (F39-E39)/E39)</f>
         <v/>
       </c>
-      <c r="H39" s="3" t="n">
-        <v>234</v>
-      </c>
+      <c r="H39" s="3" t="n"/>
       <c r="I39" s="3" t="n">
-        <v>83</v>
+        <v>9</v>
       </c>
       <c r="J39" s="6">
         <f>IF(H39=0, "N/A", (I39-H39)/H39)</f>
@@ -13964,7 +13974,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Capucha Orangutan</t>
+          <t>Buzos C Redondo Orangutan</t>
         </is>
       </c>
       <c r="B40" s="3" t="n"/>
@@ -13976,16 +13986,14 @@
         <v/>
       </c>
       <c r="E40" s="3" t="n"/>
-      <c r="F40" s="3" t="n">
-        <v>4</v>
-      </c>
+      <c r="F40" s="3" t="n"/>
       <c r="G40" s="6">
         <f>IF(E40=0, "N/A", (F40-E40)/E40)</f>
         <v/>
       </c>
       <c r="H40" s="3" t="n"/>
       <c r="I40" s="3" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="J40" s="6">
         <f>IF(H40=0, "N/A", (I40-H40)/H40)</f>
@@ -14007,13 +14015,13 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Redondo Orangutan</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="n"/>
-      <c r="C41" s="3" t="n">
+          <t>Buzos C Redondo Rustico</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
         <v>1</v>
       </c>
+      <c r="C41" s="3" t="n"/>
       <c r="D41" s="6">
         <f>IF(B41=0, "N/A", (C41-B41)/B41)</f>
         <v/>
@@ -14025,9 +14033,7 @@
         <v/>
       </c>
       <c r="H41" s="3" t="n"/>
-      <c r="I41" s="3" t="n">
-        <v>18</v>
-      </c>
+      <c r="I41" s="3" t="n"/>
       <c r="J41" s="6">
         <f>IF(H41=0, "N/A", (I41-H41)/H41)</f>
         <v/>
@@ -16013,7 +16019,9 @@
           <t>Buzo C Capucha Rustico</t>
         </is>
       </c>
-      <c r="B119" s="8" t="n"/>
+      <c r="B119" s="8" t="n">
+        <v>41318.4246</v>
+      </c>
       <c r="C119" s="8" t="n"/>
       <c r="D119" s="6">
         <f>IF(B119=0, "N/A", (C119-B119)/B119)</f>
@@ -16098,25 +16106,35 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Buzos</t>
+          <t>Buzos C Capucha</t>
         </is>
       </c>
       <c r="B121" s="8" t="n">
-        <v>39999</v>
-      </c>
-      <c r="C121" s="8" t="n"/>
+        <v>2807937.2745</v>
+      </c>
+      <c r="C121" s="8" t="n">
+        <v>1301300</v>
+      </c>
       <c r="D121" s="6">
         <f>IF(B121=0, "N/A", (C121-B121)/B121)</f>
         <v/>
       </c>
-      <c r="E121" s="8" t="n"/>
-      <c r="F121" s="8" t="n"/>
+      <c r="E121" s="8" t="n">
+        <v>2215733.6125</v>
+      </c>
+      <c r="F121" s="8" t="n">
+        <v>2119527.1668</v>
+      </c>
       <c r="G121" s="6">
         <f>IF(E121=0, "N/A", (F121-E121)/E121)</f>
         <v/>
       </c>
-      <c r="H121" s="8" t="n"/>
-      <c r="I121" s="8" t="n"/>
+      <c r="H121" s="8" t="n">
+        <v>13138531.5353</v>
+      </c>
+      <c r="I121" s="8" t="n">
+        <v>4786654.8891</v>
+      </c>
       <c r="J121" s="6">
         <f>IF(H121=0, "N/A", (I121-H121)/H121)</f>
         <v/>
@@ -16137,34 +16155,28 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Capucha</t>
-        </is>
-      </c>
-      <c r="B122" s="8" t="n">
-        <v>2849255.6991</v>
-      </c>
+          <t>Buzos C Capucha Orangutan</t>
+        </is>
+      </c>
+      <c r="B122" s="8" t="n"/>
       <c r="C122" s="8" t="n">
-        <v>1301300</v>
+        <v>52900</v>
       </c>
       <c r="D122" s="6">
         <f>IF(B122=0, "N/A", (C122-B122)/B122)</f>
         <v/>
       </c>
-      <c r="E122" s="8" t="n">
-        <v>2215733.6125</v>
-      </c>
+      <c r="E122" s="8" t="n"/>
       <c r="F122" s="8" t="n">
-        <v>2119527.1668</v>
+        <v>211031.3798</v>
       </c>
       <c r="G122" s="6">
         <f>IF(E122=0, "N/A", (F122-E122)/E122)</f>
         <v/>
       </c>
-      <c r="H122" s="8" t="n">
-        <v>13138531.5353</v>
-      </c>
+      <c r="H122" s="8" t="n"/>
       <c r="I122" s="8" t="n">
-        <v>4786654.8891</v>
+        <v>476100</v>
       </c>
       <c r="J122" s="6">
         <f>IF(H122=0, "N/A", (I122-H122)/H122)</f>
@@ -16186,28 +16198,26 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Capucha Orangutan</t>
+          <t>Buzos C Redondo Orangutan</t>
         </is>
       </c>
       <c r="B123" s="8" t="n"/>
       <c r="C123" s="8" t="n">
-        <v>52900</v>
+        <v>39900</v>
       </c>
       <c r="D123" s="6">
         <f>IF(B123=0, "N/A", (C123-B123)/B123)</f>
         <v/>
       </c>
       <c r="E123" s="8" t="n"/>
-      <c r="F123" s="8" t="n">
-        <v>211031.3798</v>
-      </c>
+      <c r="F123" s="8" t="n"/>
       <c r="G123" s="6">
         <f>IF(E123=0, "N/A", (F123-E123)/E123)</f>
         <v/>
       </c>
       <c r="H123" s="8" t="n"/>
       <c r="I123" s="8" t="n">
-        <v>476100</v>
+        <v>718200</v>
       </c>
       <c r="J123" s="6">
         <f>IF(H123=0, "N/A", (I123-H123)/H123)</f>
@@ -16229,13 +16239,13 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Redondo Orangutan</t>
-        </is>
-      </c>
-      <c r="B124" s="8" t="n"/>
-      <c r="C124" s="8" t="n">
-        <v>39900</v>
-      </c>
+          <t>Buzos C Redondo Rustico</t>
+        </is>
+      </c>
+      <c r="B124" s="8" t="n">
+        <v>39999</v>
+      </c>
+      <c r="C124" s="8" t="n"/>
       <c r="D124" s="6">
         <f>IF(B124=0, "N/A", (C124-B124)/B124)</f>
         <v/>
@@ -16247,9 +16257,7 @@
         <v/>
       </c>
       <c r="H124" s="8" t="n"/>
-      <c r="I124" s="8" t="n">
-        <v>718200</v>
-      </c>
+      <c r="I124" s="8" t="n"/>
       <c r="J124" s="6">
         <f>IF(H124=0, "N/A", (I124-H124)/H124)</f>
         <v/>
@@ -22694,7 +22702,9 @@
           <t>Buzo C Capucha Rustico</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n"/>
+      <c r="B35" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="C35" s="3" t="n"/>
       <c r="D35" s="6">
         <f>IF(B35=0, "N/A", (C35-B35)/B35)</f>
@@ -22781,7 +22791,7 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C37" s="3" t="n">
         <v>55</v>
@@ -24901,7 +24911,9 @@
           <t>Buzo C Capucha Rustico</t>
         </is>
       </c>
-      <c r="B119" s="8" t="n"/>
+      <c r="B119" s="8" t="n">
+        <v>39999</v>
+      </c>
       <c r="C119" s="8" t="n"/>
       <c r="D119" s="6">
         <f>IF(B119=0, "N/A", (C119-B119)/B119)</f>
@@ -24988,7 +25000,7 @@
         </is>
       </c>
       <c r="B121" s="8" t="n">
-        <v>4441963.4714</v>
+        <v>4401964.4714</v>
       </c>
       <c r="C121" s="8" t="n">
         <v>3098377.5893</v>
@@ -26474,15 +26486,21 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Buzos</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
+          <t>Buzos C Capucha</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>40</v>
+      </c>
       <c r="D6" s="3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E6" s="3" t="n"/>
+        <v>127</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="F6" s="4">
         <f>B6+C6+D6+E6</f>
         <v/>
@@ -26491,20 +26509,20 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Capucha</t>
+          <t>Buzos C Capucha Orangutan</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>127</v>
+        <v>48</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" s="4">
         <f>B7+C7+D7+E7</f>
@@ -26514,20 +26532,20 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Capucha Orangutan</t>
+          <t>Buzos C Redondo Orangutan</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F8" s="4">
         <f>B8+C8+D8+E8</f>
@@ -26537,21 +26555,15 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Redondo Orangutan</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>2</v>
-      </c>
+          <t>Buzos C Redondo Rustico</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>6</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="E9" s="3" t="n"/>
       <c r="F9" s="4">
         <f>B9+C9+D9+E9</f>
         <v/>
@@ -27163,24 +27175,34 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Buzos</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n"/>
+          <t>Buzos C Capucha</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>33</v>
+      </c>
       <c r="D34" s="6">
         <f>IF(B34=0, "N/A", (C34-B34)/B34)</f>
         <v/>
       </c>
-      <c r="E34" s="3" t="n"/>
-      <c r="F34" s="3" t="n"/>
+      <c r="E34" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>40</v>
+      </c>
       <c r="G34" s="6">
         <f>IF(E34=0, "N/A", (F34-E34)/E34)</f>
         <v/>
       </c>
-      <c r="H34" s="3" t="n"/>
+      <c r="H34" s="3" t="n">
+        <v>169</v>
+      </c>
       <c r="I34" s="3" t="n">
-        <v>-1</v>
+        <v>127</v>
       </c>
       <c r="J34" s="6">
         <f>IF(H34=0, "N/A", (I34-H34)/H34)</f>
@@ -27202,34 +27224,28 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Capucha</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="n">
-        <v>37</v>
-      </c>
+          <t>Buzos C Capucha Orangutan</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n"/>
       <c r="C35" s="3" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="D35" s="6">
         <f>IF(B35=0, "N/A", (C35-B35)/B35)</f>
         <v/>
       </c>
-      <c r="E35" s="3" t="n">
-        <v>40</v>
-      </c>
+      <c r="E35" s="3" t="n"/>
       <c r="F35" s="3" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="G35" s="6">
         <f>IF(E35=0, "N/A", (F35-E35)/E35)</f>
         <v/>
       </c>
-      <c r="H35" s="3" t="n">
-        <v>169</v>
-      </c>
+      <c r="H35" s="3" t="n"/>
       <c r="I35" s="3" t="n">
-        <v>127</v>
+        <v>48</v>
       </c>
       <c r="J35" s="6">
         <f>IF(H35=0, "N/A", (I35-H35)/H35)</f>
@@ -27251,12 +27267,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Capucha Orangutan</t>
+          <t>Buzos C Redondo Orangutan</t>
         </is>
       </c>
       <c r="B36" s="3" t="n"/>
       <c r="C36" s="3" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D36" s="6">
         <f>IF(B36=0, "N/A", (C36-B36)/B36)</f>
@@ -27264,7 +27280,7 @@
       </c>
       <c r="E36" s="3" t="n"/>
       <c r="F36" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G36" s="6">
         <f>IF(E36=0, "N/A", (F36-E36)/E36)</f>
@@ -27272,7 +27288,7 @@
       </c>
       <c r="H36" s="3" t="n"/>
       <c r="I36" s="3" t="n">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="J36" s="6">
         <f>IF(H36=0, "N/A", (I36-H36)/H36)</f>
@@ -27294,28 +27310,24 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Redondo Orangutan</t>
+          <t>Buzos C Redondo Rustico</t>
         </is>
       </c>
       <c r="B37" s="3" t="n"/>
-      <c r="C37" s="3" t="n">
-        <v>4</v>
-      </c>
+      <c r="C37" s="3" t="n"/>
       <c r="D37" s="6">
         <f>IF(B37=0, "N/A", (C37-B37)/B37)</f>
         <v/>
       </c>
       <c r="E37" s="3" t="n"/>
-      <c r="F37" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="F37" s="3" t="n"/>
       <c r="G37" s="6">
         <f>IF(E37=0, "N/A", (F37-E37)/E37)</f>
         <v/>
       </c>
       <c r="H37" s="3" t="n"/>
       <c r="I37" s="3" t="n">
-        <v>17</v>
+        <v>-1</v>
       </c>
       <c r="J37" s="6">
         <f>IF(H37=0, "N/A", (I37-H37)/H37)</f>
@@ -28581,15 +28593,21 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Buzos</t>
-        </is>
-      </c>
-      <c r="B84" s="8" t="n"/>
-      <c r="C84" s="8" t="n"/>
+          <t>Buzos C Capucha</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="n">
+        <v>1801698.1462</v>
+      </c>
+      <c r="C84" s="8" t="n">
+        <v>2327567.5518</v>
+      </c>
       <c r="D84" s="8" t="n">
-        <v>-39000</v>
-      </c>
-      <c r="E84" s="8" t="n"/>
+        <v>7939828.4042</v>
+      </c>
+      <c r="E84" s="8" t="n">
+        <v>140700</v>
+      </c>
       <c r="F84" s="9">
         <f>B84+C84+D84+E84</f>
         <v/>
@@ -28598,20 +28616,20 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Capucha</t>
+          <t>Buzos C Capucha Orangutan</t>
         </is>
       </c>
       <c r="B85" s="8" t="n">
-        <v>1801698.1462</v>
+        <v>823200.1662</v>
       </c>
       <c r="C85" s="8" t="n">
-        <v>2327567.5518</v>
+        <v>598339.2602</v>
       </c>
       <c r="D85" s="8" t="n">
-        <v>7939828.4042</v>
+        <v>2493661.0683</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>140700</v>
+        <v>179639.9973</v>
       </c>
       <c r="F85" s="9">
         <f>B85+C85+D85+E85</f>
@@ -28621,20 +28639,20 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Capucha Orangutan</t>
+          <t>Buzos C Redondo Orangutan</t>
         </is>
       </c>
       <c r="B86" s="8" t="n">
-        <v>823200.1662</v>
+        <v>159600</v>
       </c>
       <c r="C86" s="8" t="n">
-        <v>598339.2602</v>
+        <v>75800</v>
       </c>
       <c r="D86" s="8" t="n">
-        <v>2493661.0683</v>
+        <v>654876.6838</v>
       </c>
       <c r="E86" s="8" t="n">
-        <v>179639.9973</v>
+        <v>204729.9978</v>
       </c>
       <c r="F86" s="9">
         <f>B86+C86+D86+E86</f>
@@ -28644,21 +28662,15 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Redondo Orangutan</t>
-        </is>
-      </c>
-      <c r="B87" s="8" t="n">
-        <v>159600</v>
-      </c>
-      <c r="C87" s="8" t="n">
-        <v>75800</v>
-      </c>
+          <t>Buzos C Redondo Rustico</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="n"/>
+      <c r="C87" s="8" t="n"/>
       <c r="D87" s="8" t="n">
-        <v>654876.6838</v>
-      </c>
-      <c r="E87" s="8" t="n">
-        <v>204729.9978</v>
-      </c>
+        <v>-39000</v>
+      </c>
+      <c r="E87" s="8" t="n"/>
       <c r="F87" s="9">
         <f>B87+C87+D87+E87</f>
         <v/>
@@ -29270,24 +29282,34 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Buzos</t>
-        </is>
-      </c>
-      <c r="B112" s="8" t="n"/>
-      <c r="C112" s="8" t="n"/>
+          <t>Buzos C Capucha</t>
+        </is>
+      </c>
+      <c r="B112" s="8" t="n">
+        <v>1892728.2953</v>
+      </c>
+      <c r="C112" s="8" t="n">
+        <v>1801698.1462</v>
+      </c>
       <c r="D112" s="6">
         <f>IF(B112=0, "N/A", (C112-B112)/B112)</f>
         <v/>
       </c>
-      <c r="E112" s="8" t="n"/>
-      <c r="F112" s="8" t="n"/>
+      <c r="E112" s="8" t="n">
+        <v>2014933.872</v>
+      </c>
+      <c r="F112" s="8" t="n">
+        <v>2327567.5518</v>
+      </c>
       <c r="G112" s="6">
         <f>IF(E112=0, "N/A", (F112-E112)/E112)</f>
         <v/>
       </c>
-      <c r="H112" s="8" t="n"/>
+      <c r="H112" s="8" t="n">
+        <v>9196365</v>
+      </c>
       <c r="I112" s="8" t="n">
-        <v>-39000</v>
+        <v>7939828.4042</v>
       </c>
       <c r="J112" s="6">
         <f>IF(H112=0, "N/A", (I112-H112)/H112)</f>
@@ -29309,34 +29331,28 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Capucha</t>
-        </is>
-      </c>
-      <c r="B113" s="8" t="n">
-        <v>1892728.2953</v>
-      </c>
+          <t>Buzos C Capucha Orangutan</t>
+        </is>
+      </c>
+      <c r="B113" s="8" t="n"/>
       <c r="C113" s="8" t="n">
-        <v>1801698.1462</v>
+        <v>823200.1662</v>
       </c>
       <c r="D113" s="6">
         <f>IF(B113=0, "N/A", (C113-B113)/B113)</f>
         <v/>
       </c>
-      <c r="E113" s="8" t="n">
-        <v>2014933.872</v>
-      </c>
+      <c r="E113" s="8" t="n"/>
       <c r="F113" s="8" t="n">
-        <v>2327567.5518</v>
+        <v>598339.2602</v>
       </c>
       <c r="G113" s="6">
         <f>IF(E113=0, "N/A", (F113-E113)/E113)</f>
         <v/>
       </c>
-      <c r="H113" s="8" t="n">
-        <v>9196365</v>
-      </c>
+      <c r="H113" s="8" t="n"/>
       <c r="I113" s="8" t="n">
-        <v>7939828.4042</v>
+        <v>2493661.0683</v>
       </c>
       <c r="J113" s="6">
         <f>IF(H113=0, "N/A", (I113-H113)/H113)</f>
@@ -29358,12 +29374,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Capucha Orangutan</t>
+          <t>Buzos C Redondo Orangutan</t>
         </is>
       </c>
       <c r="B114" s="8" t="n"/>
       <c r="C114" s="8" t="n">
-        <v>823200.1662</v>
+        <v>159600</v>
       </c>
       <c r="D114" s="6">
         <f>IF(B114=0, "N/A", (C114-B114)/B114)</f>
@@ -29371,7 +29387,7 @@
       </c>
       <c r="E114" s="8" t="n"/>
       <c r="F114" s="8" t="n">
-        <v>598339.2602</v>
+        <v>75800</v>
       </c>
       <c r="G114" s="6">
         <f>IF(E114=0, "N/A", (F114-E114)/E114)</f>
@@ -29379,7 +29395,7 @@
       </c>
       <c r="H114" s="8" t="n"/>
       <c r="I114" s="8" t="n">
-        <v>2493661.0683</v>
+        <v>654876.6838</v>
       </c>
       <c r="J114" s="6">
         <f>IF(H114=0, "N/A", (I114-H114)/H114)</f>
@@ -29401,28 +29417,24 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Redondo Orangutan</t>
+          <t>Buzos C Redondo Rustico</t>
         </is>
       </c>
       <c r="B115" s="8" t="n"/>
-      <c r="C115" s="8" t="n">
-        <v>159600</v>
-      </c>
+      <c r="C115" s="8" t="n"/>
       <c r="D115" s="6">
         <f>IF(B115=0, "N/A", (C115-B115)/B115)</f>
         <v/>
       </c>
       <c r="E115" s="8" t="n"/>
-      <c r="F115" s="8" t="n">
-        <v>75800</v>
-      </c>
+      <c r="F115" s="8" t="n"/>
       <c r="G115" s="6">
         <f>IF(E115=0, "N/A", (F115-E115)/E115)</f>
         <v/>
       </c>
       <c r="H115" s="8" t="n"/>
       <c r="I115" s="8" t="n">
-        <v>654876.6838</v>
+        <v>-39000</v>
       </c>
       <c r="J115" s="6">
         <f>IF(H115=0, "N/A", (I115-H115)/H115)</f>
@@ -30608,7 +30620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M156"/>
+  <dimension ref="A1:M160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -30727,21 +30739,15 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Buzo Cuello Redondo</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>14</v>
-      </c>
+          <t>Buzo C Capucha Rustico</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
       <c r="D6" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E6" s="3" t="n"/>
       <c r="F6" s="4">
         <f>B6+C6+D6+E6</f>
         <v/>
@@ -30750,15 +30756,21 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Buzos</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
+          <t>Buzo Cuello Redondo</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>14</v>
+      </c>
       <c r="D7" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" s="3" t="n"/>
+        <v>70</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="F7" s="4">
         <f>B7+C7+D7+E7</f>
         <v/>
@@ -30777,7 +30789,7 @@
         <v>7</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="4">
@@ -30834,13 +30846,13 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Buzos Medio Cierre</t>
+          <t>Buzos C Redondo Rustico</t>
         </is>
       </c>
       <c r="B11" s="3" t="n"/>
       <c r="C11" s="3" t="n"/>
       <c r="D11" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="4">
@@ -30851,7 +30863,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Calzado</t>
+          <t>Buzos Medio Cierre</t>
         </is>
       </c>
       <c r="B12" s="3" t="n"/>
@@ -30868,16 +30880,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Camisas</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" s="3" t="n"/>
+          <t>Calzado</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="E13" s="3" t="n"/>
       <c r="F13" s="4">
         <f>B13+C13+D13+E13</f>
@@ -30887,18 +30897,16 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Camisetas Manga Larga</t>
+          <t>Camisas</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="D14" s="3" t="n">
         <v>2</v>
       </c>
+      <c r="D14" s="3" t="n"/>
       <c r="E14" s="3" t="n"/>
       <c r="F14" s="4">
         <f>B14+C14+D14+E14</f>
@@ -30908,17 +30916,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Camisetas Manga Larga Orangutan</t>
+          <t>Camisetas Manga Larga</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D15" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>14</v>
       </c>
       <c r="E15" s="3" t="n"/>
       <c r="F15" s="4">
@@ -30929,15 +30937,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Campera S Capucha</t>
+          <t>Camisetas Manga Larga Orangutan</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" s="3" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="D16" s="3" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E16" s="3" t="n"/>
       <c r="F16" s="4">
@@ -30948,17 +30958,15 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Camperas Capucha</t>
+          <t>Campera S Capucha</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>7</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="4">
@@ -30969,17 +30977,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Camperas De Abrigo</t>
+          <t>Camperas Capucha</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>-7</v>
+        <v>7</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E18" s="3" t="n"/>
       <c r="F18" s="4">
@@ -30990,17 +30998,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Chombas</t>
+          <t>Camperas De Abrigo</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E19" s="3" t="n"/>
       <c r="F19" s="4">
@@ -31011,16 +31019,18 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Chombas Manga Larga</t>
+          <t>Chombas</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C20" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D20" s="3" t="n"/>
       <c r="E20" s="3" t="n"/>
       <c r="F20" s="4">
         <f>B20+C20+D20+E20</f>
@@ -31030,15 +31040,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Detroit</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
+          <t>Chombas Manga Larga</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="E21" s="3" t="n"/>
       <c r="F21" s="4">
         <f>B21+C21+D21+E21</f>
         <v/>
@@ -31047,20 +31059,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Jeans</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>158</v>
-      </c>
+          <t>Detroit</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="3" t="n"/>
       <c r="E22" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F22" s="4">
         <f>B22+C22+D22+E22</f>
@@ -31070,17 +31076,21 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Jogging</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n"/>
+          <t>Jeans</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>18</v>
+      </c>
       <c r="C23" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="E23" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D23" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="E23" s="3" t="n"/>
       <c r="F23" s="4">
         <f>B23+C23+D23+E23</f>
         <v/>
@@ -31089,21 +31099,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Remeras</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>10</v>
-      </c>
+          <t>Jogging</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n"/>
       <c r="C24" s="3" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>3</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="E24" s="3" t="n"/>
       <c r="F24" s="4">
         <f>B24+C24+D24+E24</f>
         <v/>
@@ -31112,210 +31118,194 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Sweaters</t>
+          <t>Remeras</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="E25" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C25" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="3" t="n"/>
       <c r="F25" s="4">
         <f>B25+C25+D25+E25</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Sweaters</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="4">
+        <f>B26+C26+D26+E26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>Totals</t>
         </is>
       </c>
-      <c r="B26" s="4">
-        <f>SUM($B$3:$B$25)</f>
-        <v/>
-      </c>
-      <c r="C26" s="4">
-        <f>SUM($C$3:$C$25)</f>
-        <v/>
-      </c>
-      <c r="D26" s="4">
-        <f>SUM($D$3:$D$25)</f>
-        <v/>
-      </c>
-      <c r="E26" s="4">
-        <f>SUM($E$3:$E$25)</f>
-        <v/>
-      </c>
-      <c r="F26" s="4">
-        <f>SUM($F$3:$F$25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="B27" s="4">
+        <f>SUM($B$3:$B$26)</f>
+        <v/>
+      </c>
+      <c r="C27" s="4">
+        <f>SUM($C$3:$C$26)</f>
+        <v/>
+      </c>
+      <c r="D27" s="4">
+        <f>SUM($D$3:$D$26)</f>
+        <v/>
+      </c>
+      <c r="E27" s="4">
+        <f>SUM($E$3:$E$26)</f>
+        <v/>
+      </c>
+      <c r="F27" s="4">
+        <f>SUM($F$3:$F$26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>YoY Units Sold Comparison - Branch Group 1</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="1" t="inlineStr">
+    <row r="31">
+      <c r="B31" s="1" t="inlineStr">
         <is>
           <t>LIBERT.R</t>
         </is>
       </c>
-      <c r="C30" s="1" t="n"/>
-      <c r="D30" s="1" t="n"/>
-      <c r="E30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="n"/>
+      <c r="D31" s="1" t="n"/>
+      <c r="E31" s="1" t="inlineStr">
         <is>
           <t>PASO.R</t>
         </is>
       </c>
-      <c r="F30" s="1" t="n"/>
-      <c r="G30" s="1" t="n"/>
-      <c r="H30" s="1" t="inlineStr">
+      <c r="F31" s="1" t="n"/>
+      <c r="G31" s="1" t="n"/>
+      <c r="H31" s="1" t="inlineStr">
         <is>
           <t>P.OESTE</t>
         </is>
       </c>
-      <c r="I30" s="1" t="n"/>
-      <c r="J30" s="1" t="n"/>
-      <c r="K30" s="1" t="inlineStr">
+      <c r="I31" s="1" t="n"/>
+      <c r="J31" s="1" t="n"/>
+      <c r="K31" s="1" t="inlineStr">
         <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="L30" s="1" t="n"/>
-      <c r="M30" s="1" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="L31" s="1" t="n"/>
+      <c r="M31" s="1" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>Familias</t>
         </is>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B32" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C32" s="1" t="n">
         <v>2026</v>
       </c>
-      <c r="D31" s="1" t="inlineStr">
+      <c r="D32" s="1" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E31" s="1" t="n">
+      <c r="E32" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="F31" s="1" t="n">
+      <c r="F32" s="1" t="n">
         <v>2026</v>
       </c>
-      <c r="G31" s="1" t="inlineStr">
+      <c r="G32" s="1" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H31" s="1" t="n">
+      <c r="H32" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="I31" s="1" t="n">
+      <c r="I32" s="1" t="n">
         <v>2026</v>
       </c>
-      <c r="J31" s="1" t="inlineStr">
+      <c r="J32" s="1" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="K31" s="1" t="n">
+      <c r="K32" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="L31" s="1" t="n">
+      <c r="L32" s="1" t="n">
         <v>2026</v>
       </c>
-      <c r="M31" s="1" t="inlineStr">
+      <c r="M32" s="1" t="inlineStr">
         <is>
           <t>%</t>
         </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Accesorios</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C32" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D32" s="6">
-        <f>IF(B32=0, "N/A", (C32-B32)/B32)</f>
-        <v/>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G32" s="6">
-        <f>IF(E32=0, "N/A", (F32-E32)/E32)</f>
-        <v/>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="I32" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="J32" s="6">
-        <f>IF(H32=0, "N/A", (I32-H32)/H32)</f>
-        <v/>
-      </c>
-      <c r="K32" s="3">
-        <f>B32+E32+H32</f>
-        <v/>
-      </c>
-      <c r="L32" s="3">
-        <f>C32+F32+I32</f>
-        <v/>
-      </c>
-      <c r="M32" s="6">
-        <f>IF(K32=0, "N/A", (L32-K32)/K32)</f>
-        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Bermudas</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="n"/>
-      <c r="C33" s="3" t="n"/>
+          <t>Accesorios</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="D33" s="6">
         <f>IF(B33=0, "N/A", (C33-B33)/B33)</f>
         <v/>
       </c>
-      <c r="E33" s="3" t="n"/>
+      <c r="E33" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="F33" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G33" s="6">
         <f>IF(E33=0, "N/A", (F33-E33)/E33)</f>
         <v/>
       </c>
-      <c r="H33" s="3" t="n"/>
-      <c r="I33" s="3" t="n"/>
+      <c r="H33" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>32</v>
+      </c>
       <c r="J33" s="6">
         <f>IF(H33=0, "N/A", (I33-H33)/H33)</f>
         <v/>
@@ -31336,33 +31326,25 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Boxer</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C34" s="3" t="n">
-        <v>5</v>
-      </c>
+          <t>Bermudas</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="3" t="n"/>
       <c r="D34" s="6">
         <f>IF(B34=0, "N/A", (C34-B34)/B34)</f>
         <v/>
       </c>
       <c r="E34" s="3" t="n"/>
       <c r="F34" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G34" s="6">
         <f>IF(E34=0, "N/A", (F34-E34)/E34)</f>
         <v/>
       </c>
-      <c r="H34" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="I34" s="3" t="n">
-        <v>19</v>
-      </c>
+      <c r="H34" s="3" t="n"/>
+      <c r="I34" s="3" t="n"/>
       <c r="J34" s="6">
         <f>IF(H34=0, "N/A", (I34-H34)/H34)</f>
         <v/>
@@ -31383,34 +31365,32 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Buzo Cuello Redondo</t>
+          <t>Boxer</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D35" s="6">
         <f>IF(B35=0, "N/A", (C35-B35)/B35)</f>
         <v/>
       </c>
-      <c r="E35" s="3" t="n">
-        <v>41</v>
-      </c>
+      <c r="E35" s="3" t="n"/>
       <c r="F35" s="3" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G35" s="6">
         <f>IF(E35=0, "N/A", (F35-E35)/E35)</f>
         <v/>
       </c>
       <c r="H35" s="3" t="n">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="J35" s="6">
         <f>IF(H35=0, "N/A", (I35-H35)/H35)</f>
@@ -31432,7 +31412,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Buzos</t>
+          <t>Buzo C Capucha Rustico</t>
         </is>
       </c>
       <c r="B36" s="3" t="n"/>
@@ -31449,7 +31429,7 @@
       </c>
       <c r="H36" s="3" t="n"/>
       <c r="I36" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J36" s="6">
         <f>IF(H36=0, "N/A", (I36-H36)/H36)</f>
@@ -31471,34 +31451,34 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Capucha</t>
+          <t>Buzo Cuello Redondo</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>21</v>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>12</v>
       </c>
       <c r="D37" s="6">
         <f>IF(B37=0, "N/A", (C37-B37)/B37)</f>
         <v/>
       </c>
       <c r="E37" s="3" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G37" s="6">
         <f>IF(E37=0, "N/A", (F37-E37)/E37)</f>
         <v/>
       </c>
       <c r="H37" s="3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="J37" s="6">
         <f>IF(H37=0, "N/A", (I37-H37)/H37)</f>
@@ -31520,28 +31500,34 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Capucha Orangutan</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="n"/>
+          <t>Buzos C Capucha</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>21</v>
+      </c>
       <c r="C38" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D38" s="6">
         <f>IF(B38=0, "N/A", (C38-B38)/B38)</f>
         <v/>
       </c>
-      <c r="E38" s="3" t="n"/>
+      <c r="E38" s="3" t="n">
+        <v>23</v>
+      </c>
       <c r="F38" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G38" s="6">
         <f>IF(E38=0, "N/A", (F38-E38)/E38)</f>
         <v/>
       </c>
-      <c r="H38" s="3" t="n"/>
+      <c r="H38" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="I38" s="3" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J38" s="6">
         <f>IF(H38=0, "N/A", (I38-H38)/H38)</f>
@@ -31563,12 +31549,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Redondo Orangutan</t>
+          <t>Buzos C Capucha Orangutan</t>
         </is>
       </c>
       <c r="B39" s="3" t="n"/>
       <c r="C39" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39" s="6">
         <f>IF(B39=0, "N/A", (C39-B39)/B39)</f>
@@ -31576,7 +31562,7 @@
       </c>
       <c r="E39" s="3" t="n"/>
       <c r="F39" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G39" s="6">
         <f>IF(E39=0, "N/A", (F39-E39)/E39)</f>
@@ -31584,7 +31570,7 @@
       </c>
       <c r="H39" s="3" t="n"/>
       <c r="I39" s="3" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="J39" s="6">
         <f>IF(H39=0, "N/A", (I39-H39)/H39)</f>
@@ -31606,28 +31592,28 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Buzos Medio Cierre</t>
+          <t>Buzos C Redondo Orangutan</t>
         </is>
       </c>
       <c r="B40" s="3" t="n"/>
-      <c r="C40" s="3" t="n"/>
+      <c r="C40" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="D40" s="6">
         <f>IF(B40=0, "N/A", (C40-B40)/B40)</f>
         <v/>
       </c>
-      <c r="E40" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F40" s="3" t="n"/>
+      <c r="E40" s="3" t="n"/>
+      <c r="F40" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="G40" s="6">
         <f>IF(E40=0, "N/A", (F40-E40)/E40)</f>
         <v/>
       </c>
-      <c r="H40" s="3" t="n">
-        <v>-1</v>
-      </c>
+      <c r="H40" s="3" t="n"/>
       <c r="I40" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J40" s="6">
         <f>IF(H40=0, "N/A", (I40-H40)/H40)</f>
@@ -31649,7 +31635,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Calzado</t>
+          <t>Buzos C Redondo Rustico</t>
         </is>
       </c>
       <c r="B41" s="3" t="n"/>
@@ -31666,7 +31652,7 @@
       </c>
       <c r="H41" s="3" t="n"/>
       <c r="I41" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J41" s="6">
         <f>IF(H41=0, "N/A", (I41-H41)/H41)</f>
@@ -31688,33 +31674,29 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Camisas</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C42" s="3" t="n">
-        <v>5</v>
-      </c>
+          <t>Buzos Medio Cierre</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n"/>
+      <c r="C42" s="3" t="n"/>
       <c r="D42" s="6">
         <f>IF(B42=0, "N/A", (C42-B42)/B42)</f>
         <v/>
       </c>
       <c r="E42" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="3" t="n">
         <v>2</v>
       </c>
+      <c r="F42" s="3" t="n"/>
       <c r="G42" s="6">
         <f>IF(E42=0, "N/A", (F42-E42)/E42)</f>
         <v/>
       </c>
       <c r="H42" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="I42" s="3" t="n"/>
+        <v>-1</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J42" s="6">
         <f>IF(H42=0, "N/A", (I42-H42)/H42)</f>
         <v/>
@@ -31735,34 +31717,24 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Camisetas Manga Larga</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="C43" s="3" t="n">
-        <v>9</v>
-      </c>
+          <t>Calzado</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n"/>
+      <c r="C43" s="3" t="n"/>
       <c r="D43" s="6">
         <f>IF(B43=0, "N/A", (C43-B43)/B43)</f>
         <v/>
       </c>
-      <c r="E43" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>11</v>
-      </c>
+      <c r="E43" s="3" t="n"/>
+      <c r="F43" s="3" t="n"/>
       <c r="G43" s="6">
         <f>IF(E43=0, "N/A", (F43-E43)/E43)</f>
         <v/>
       </c>
-      <c r="H43" s="3" t="n">
-        <v>16</v>
-      </c>
+      <c r="H43" s="3" t="n"/>
       <c r="I43" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J43" s="6">
         <f>IF(H43=0, "N/A", (I43-H43)/H43)</f>
@@ -31784,18 +31756,22 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Camisetas Manga Larga Orangutan</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="n"/>
+          <t>Camisas</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="C44" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D44" s="6">
         <f>IF(B44=0, "N/A", (C44-B44)/B44)</f>
         <v/>
       </c>
-      <c r="E44" s="3" t="n"/>
+      <c r="E44" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="F44" s="3" t="n">
         <v>2</v>
       </c>
@@ -31803,10 +31779,10 @@
         <f>IF(E44=0, "N/A", (F44-E44)/E44)</f>
         <v/>
       </c>
-      <c r="H44" s="3" t="n"/>
-      <c r="I44" s="3" t="n">
-        <v>14</v>
-      </c>
+      <c r="H44" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I44" s="3" t="n"/>
       <c r="J44" s="6">
         <f>IF(H44=0, "N/A", (I44-H44)/H44)</f>
         <v/>
@@ -31827,29 +31803,31 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Campera S Capucha</t>
+          <t>Camisetas Manga Larga</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D45" s="6">
         <f>IF(B45=0, "N/A", (C45-B45)/B45)</f>
         <v/>
       </c>
       <c r="E45" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" s="3" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>11</v>
+      </c>
       <c r="G45" s="6">
         <f>IF(E45=0, "N/A", (F45-E45)/E45)</f>
         <v/>
       </c>
       <c r="H45" s="3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I45" s="3" t="n">
         <v>2</v>
@@ -31874,34 +31852,28 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Camperas Capucha</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="n">
+          <t>Camisetas Manga Larga Orangutan</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n"/>
+      <c r="C46" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="C46" s="3" t="n">
-        <v>4</v>
       </c>
       <c r="D46" s="6">
         <f>IF(B46=0, "N/A", (C46-B46)/B46)</f>
         <v/>
       </c>
-      <c r="E46" s="3" t="n">
-        <v>-1</v>
-      </c>
+      <c r="E46" s="3" t="n"/>
       <c r="F46" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G46" s="6">
         <f>IF(E46=0, "N/A", (F46-E46)/E46)</f>
         <v/>
       </c>
-      <c r="H46" s="3" t="n">
-        <v>16</v>
-      </c>
+      <c r="H46" s="3" t="n"/>
       <c r="I46" s="3" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="J46" s="6">
         <f>IF(H46=0, "N/A", (I46-H46)/H46)</f>
@@ -31923,34 +31895,32 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Camperas De Abrigo</t>
+          <t>Campera S Capucha</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D47" s="6">
         <f>IF(B47=0, "N/A", (C47-B47)/B47)</f>
         <v/>
       </c>
       <c r="E47" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>-7</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F47" s="3" t="n"/>
       <c r="G47" s="6">
         <f>IF(E47=0, "N/A", (F47-E47)/E47)</f>
         <v/>
       </c>
       <c r="H47" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J47" s="6">
         <f>IF(H47=0, "N/A", (I47-H47)/H47)</f>
@@ -31972,11 +31942,11 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Chombas</t>
+          <t>Camperas Capucha</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>4</v>
@@ -31986,20 +31956,20 @@
         <v/>
       </c>
       <c r="E48" s="3" t="n">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G48" s="6">
         <f>IF(E48=0, "N/A", (F48-E48)/E48)</f>
         <v/>
       </c>
       <c r="H48" s="3" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="J48" s="6">
         <f>IF(H48=0, "N/A", (I48-H48)/H48)</f>
@@ -32021,27 +31991,35 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Chombas Manga Larga</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="n"/>
+          <t>Camperas De Abrigo</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>13</v>
+      </c>
       <c r="C49" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" s="6">
         <f>IF(B49=0, "N/A", (C49-B49)/B49)</f>
         <v/>
       </c>
-      <c r="E49" s="3" t="n"/>
+      <c r="E49" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="F49" s="3" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
       <c r="G49" s="6">
         <f>IF(E49=0, "N/A", (F49-E49)/E49)</f>
         <v/>
       </c>
-      <c r="H49" s="3" t="n"/>
-      <c r="I49" s="3" t="n"/>
+      <c r="H49" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>9</v>
+      </c>
       <c r="J49" s="6">
         <f>IF(H49=0, "N/A", (I49-H49)/H49)</f>
         <v/>
@@ -32062,34 +32040,34 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Jeans</t>
+          <t>Chombas</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D50" s="6">
         <f>IF(B50=0, "N/A", (C50-B50)/B50)</f>
         <v/>
       </c>
       <c r="E50" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="G50" s="6">
         <f>IF(E50=0, "N/A", (F50-E50)/E50)</f>
         <v/>
       </c>
       <c r="H50" s="3" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>158</v>
+        <v>3</v>
       </c>
       <c r="J50" s="6">
         <f>IF(H50=0, "N/A", (I50-H50)/H50)</f>
@@ -32111,33 +32089,27 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Jogging</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C51" s="3" t="n"/>
+          <t>Chombas Manga Larga</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n"/>
+      <c r="C51" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="D51" s="6">
         <f>IF(B51=0, "N/A", (C51-B51)/B51)</f>
         <v/>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="E51" s="3" t="n"/>
+      <c r="F51" s="3" t="n">
         <v>3</v>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>4</v>
       </c>
       <c r="G51" s="6">
         <f>IF(E51=0, "N/A", (F51-E51)/E51)</f>
         <v/>
       </c>
-      <c r="H51" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="I51" s="3" t="n">
-        <v>7</v>
-      </c>
+      <c r="H51" s="3" t="n"/>
+      <c r="I51" s="3" t="n"/>
       <c r="J51" s="6">
         <f>IF(H51=0, "N/A", (I51-H51)/H51)</f>
         <v/>
@@ -32158,27 +32130,35 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Jeans</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C52" s="3" t="n"/>
+        <v>30</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>18</v>
+      </c>
       <c r="D52" s="6">
         <f>IF(B52=0, "N/A", (C52-B52)/B52)</f>
         <v/>
       </c>
       <c r="E52" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F52" s="3" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>24</v>
+      </c>
       <c r="G52" s="6">
         <f>IF(E52=0, "N/A", (F52-E52)/E52)</f>
         <v/>
       </c>
-      <c r="H52" s="3" t="n"/>
-      <c r="I52" s="3" t="n"/>
+      <c r="H52" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="I52" s="3" t="n">
+        <v>158</v>
+      </c>
       <c r="J52" s="6">
         <f>IF(H52=0, "N/A", (I52-H52)/H52)</f>
         <v/>
@@ -32199,34 +32179,32 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Remeras</t>
+          <t>Jogging</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="C53" s="3" t="n">
-        <v>10</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="C53" s="3" t="n"/>
       <c r="D53" s="6">
         <f>IF(B53=0, "N/A", (C53-B53)/B53)</f>
         <v/>
       </c>
       <c r="E53" s="3" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="G53" s="6">
         <f>IF(E53=0, "N/A", (F53-E53)/E53)</f>
         <v/>
       </c>
       <c r="H53" s="3" t="n">
-        <v>149</v>
+        <v>5</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>125</v>
+        <v>7</v>
       </c>
       <c r="J53" s="6">
         <f>IF(H53=0, "N/A", (I53-H53)/H53)</f>
@@ -32248,35 +32226,27 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Sweaters</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C54" s="3" t="n">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C54" s="3" t="n"/>
       <c r="D54" s="6">
         <f>IF(B54=0, "N/A", (C54-B54)/B54)</f>
         <v/>
       </c>
       <c r="E54" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F54" s="3" t="n">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F54" s="3" t="n"/>
       <c r="G54" s="6">
         <f>IF(E54=0, "N/A", (F54-E54)/E54)</f>
         <v/>
       </c>
-      <c r="H54" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="I54" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="H54" s="3" t="n"/>
+      <c r="I54" s="3" t="n"/>
       <c r="J54" s="6">
         <f>IF(H54=0, "N/A", (I54-H54)/H54)</f>
         <v/>
@@ -32297,25 +32267,35 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Trajes De Baño</t>
+          <t>Remeras</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C55" s="3" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>10</v>
+      </c>
       <c r="D55" s="6">
         <f>IF(B55=0, "N/A", (C55-B55)/B55)</f>
         <v/>
       </c>
-      <c r="E55" s="3" t="n"/>
-      <c r="F55" s="3" t="n"/>
+      <c r="E55" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>48</v>
+      </c>
       <c r="G55" s="6">
         <f>IF(E55=0, "N/A", (F55-E55)/E55)</f>
         <v/>
       </c>
-      <c r="H55" s="3" t="n"/>
-      <c r="I55" s="3" t="n"/>
+      <c r="H55" s="3" t="n">
+        <v>149</v>
+      </c>
+      <c r="I55" s="3" t="n">
+        <v>125</v>
+      </c>
       <c r="J55" s="6">
         <f>IF(H55=0, "N/A", (I55-H55)/H55)</f>
         <v/>
@@ -32334,134 +32314,192 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Sweaters</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D56" s="6">
+        <f>IF(B56=0, "N/A", (C56-B56)/B56)</f>
+        <v/>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G56" s="6">
+        <f>IF(E56=0, "N/A", (F56-E56)/E56)</f>
+        <v/>
+      </c>
+      <c r="H56" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="I56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" s="6">
+        <f>IF(H56=0, "N/A", (I56-H56)/H56)</f>
+        <v/>
+      </c>
+      <c r="K56" s="3">
+        <f>B56+E56+H56</f>
+        <v/>
+      </c>
+      <c r="L56" s="3">
+        <f>C56+F56+I56</f>
+        <v/>
+      </c>
+      <c r="M56" s="6">
+        <f>IF(K56=0, "N/A", (L56-K56)/K56)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Trajes De Baño</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C57" s="3" t="n"/>
+      <c r="D57" s="6">
+        <f>IF(B57=0, "N/A", (C57-B57)/B57)</f>
+        <v/>
+      </c>
+      <c r="E57" s="3" t="n"/>
+      <c r="F57" s="3" t="n"/>
+      <c r="G57" s="6">
+        <f>IF(E57=0, "N/A", (F57-E57)/E57)</f>
+        <v/>
+      </c>
+      <c r="H57" s="3" t="n"/>
+      <c r="I57" s="3" t="n"/>
+      <c r="J57" s="6">
+        <f>IF(H57=0, "N/A", (I57-H57)/H57)</f>
+        <v/>
+      </c>
+      <c r="K57" s="3">
+        <f>B57+E57+H57</f>
+        <v/>
+      </c>
+      <c r="L57" s="3">
+        <f>C57+F57+I57</f>
+        <v/>
+      </c>
+      <c r="M57" s="6">
+        <f>IF(K57=0, "N/A", (L57-K57)/K57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>Totals</t>
         </is>
       </c>
-      <c r="B56" s="4">
-        <f>SUM($B32:$B55)</f>
-        <v/>
-      </c>
-      <c r="C56" s="4">
-        <f>SUM($C32:$C55)</f>
-        <v/>
-      </c>
-      <c r="D56" s="7">
-        <f>IF(B56=0, "N/A", (C56-B56)/B56)</f>
-        <v/>
-      </c>
-      <c r="E56" s="4">
-        <f>SUM($E32:$E55)</f>
-        <v/>
-      </c>
-      <c r="F56" s="4">
-        <f>SUM($F32:$F55)</f>
-        <v/>
-      </c>
-      <c r="G56" s="7">
-        <f>IF(E56=0, "N/A", (F56-E56)/E56)</f>
-        <v/>
-      </c>
-      <c r="H56" s="4">
-        <f>SUM($H32:$H55)</f>
-        <v/>
-      </c>
-      <c r="I56" s="4">
-        <f>SUM($I32:$I55)</f>
-        <v/>
-      </c>
-      <c r="J56" s="7">
-        <f>IF(H56=0, "N/A", (I56-H56)/H56)</f>
-        <v/>
-      </c>
-      <c r="K56" s="4">
-        <f>SUM($K32:$K55)</f>
-        <v/>
-      </c>
-      <c r="L56" s="4">
-        <f>SUM($L32:$L55)</f>
-        <v/>
-      </c>
-      <c r="M56" s="7">
-        <f>IF(K56=0, "N/A", (L56-K56)/K56)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="inlineStr">
-        <is>
-          <t>YoY Units Sold Comparison - Branch Group 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>VIRREYES</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="n"/>
-      <c r="D60" s="1" t="n"/>
+      <c r="B58" s="4">
+        <f>SUM($B33:$B57)</f>
+        <v/>
+      </c>
+      <c r="C58" s="4">
+        <f>SUM($C33:$C57)</f>
+        <v/>
+      </c>
+      <c r="D58" s="7">
+        <f>IF(B58=0, "N/A", (C58-B58)/B58)</f>
+        <v/>
+      </c>
+      <c r="E58" s="4">
+        <f>SUM($E33:$E57)</f>
+        <v/>
+      </c>
+      <c r="F58" s="4">
+        <f>SUM($F33:$F57)</f>
+        <v/>
+      </c>
+      <c r="G58" s="7">
+        <f>IF(E58=0, "N/A", (F58-E58)/E58)</f>
+        <v/>
+      </c>
+      <c r="H58" s="4">
+        <f>SUM($H33:$H57)</f>
+        <v/>
+      </c>
+      <c r="I58" s="4">
+        <f>SUM($I33:$I57)</f>
+        <v/>
+      </c>
+      <c r="J58" s="7">
+        <f>IF(H58=0, "N/A", (I58-H58)/H58)</f>
+        <v/>
+      </c>
+      <c r="K58" s="4">
+        <f>SUM($K33:$K57)</f>
+        <v/>
+      </c>
+      <c r="L58" s="4">
+        <f>SUM($L33:$L57)</f>
+        <v/>
+      </c>
+      <c r="M58" s="7">
+        <f>IF(K58=0, "N/A", (L58-K58)/K58)</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
+          <t>YoY Units Sold Comparison - Branch Group 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="1" t="inlineStr">
+        <is>
+          <t>VIRREYES</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="n"/>
+      <c r="D62" s="1" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
           <t>Familias</t>
         </is>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B63" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C63" s="1" t="n">
         <v>2026</v>
       </c>
-      <c r="D61" s="1" t="inlineStr">
+      <c r="D63" s="1" t="inlineStr">
         <is>
           <t>%</t>
         </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>Accesorios</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C62" s="3" t="n"/>
-      <c r="D62" s="6">
-        <f>IF(B62=0, "N/A", (C62-B62)/B62)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>Boxer</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C63" s="3" t="n"/>
-      <c r="D63" s="6">
-        <f>IF(B63=0, "N/A", (C63-B63)/B63)</f>
-        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Buzo Cuello Redondo</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="n"/>
-      <c r="C64" s="3" t="n">
-        <v>1</v>
-      </c>
+          <t>Accesorios</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C64" s="3" t="n"/>
       <c r="D64" s="6">
         <f>IF(B64=0, "N/A", (C64-B64)/B64)</f>
         <v/>
@@ -32470,11 +32508,11 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Capucha</t>
+          <t>Boxer</t>
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C65" s="3" t="n"/>
       <c r="D65" s="6">
@@ -32485,12 +32523,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Capucha Orangutan</t>
+          <t>Buzo Cuello Redondo</t>
         </is>
       </c>
       <c r="B66" s="3" t="n"/>
       <c r="C66" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D66" s="6">
         <f>IF(B66=0, "N/A", (C66-B66)/B66)</f>
@@ -32500,13 +32538,13 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Redondo Orangutan</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="n"/>
-      <c r="C67" s="3" t="n">
-        <v>2</v>
-      </c>
+          <t>Buzos C Capucha</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C67" s="3" t="n"/>
       <c r="D67" s="6">
         <f>IF(B67=0, "N/A", (C67-B67)/B67)</f>
         <v/>
@@ -32515,13 +32553,13 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Buzos Medio Cierre</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C68" s="3" t="n"/>
+          <t>Buzos C Capucha Orangutan</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n"/>
+      <c r="C68" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="D68" s="6">
         <f>IF(B68=0, "N/A", (C68-B68)/B68)</f>
         <v/>
@@ -32530,13 +32568,13 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Camisas</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="n">
+          <t>Buzos C Redondo Orangutan</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n"/>
+      <c r="C69" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C69" s="3" t="n"/>
       <c r="D69" s="6">
         <f>IF(B69=0, "N/A", (C69-B69)/B69)</f>
         <v/>
@@ -32545,7 +32583,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Camperas Capucha</t>
+          <t>Buzos Medio Cierre</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
@@ -32560,10 +32598,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Camperas De Abrigo</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="n"/>
+          <t>Camisas</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="C71" s="3" t="n"/>
       <c r="D71" s="6">
         <f>IF(B71=0, "N/A", (C71-B71)/B71)</f>
@@ -32573,13 +32613,13 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Detroit</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="n"/>
-      <c r="C72" s="3" t="n">
+          <t>Camperas Capucha</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
         <v>1</v>
       </c>
+      <c r="C72" s="3" t="n"/>
       <c r="D72" s="6">
         <f>IF(B72=0, "N/A", (C72-B72)/B72)</f>
         <v/>
@@ -32588,15 +32628,11 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Jeans</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C73" s="3" t="n">
-        <v>4</v>
-      </c>
+          <t>Camperas De Abrigo</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n"/>
+      <c r="C73" s="3" t="n"/>
       <c r="D73" s="6">
         <f>IF(B73=0, "N/A", (C73-B73)/B73)</f>
         <v/>
@@ -32605,13 +32641,13 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Jogging</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="n">
+          <t>Detroit</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n"/>
+      <c r="C74" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C74" s="3" t="n"/>
       <c r="D74" s="6">
         <f>IF(B74=0, "N/A", (C74-B74)/B74)</f>
         <v/>
@@ -32620,14 +32656,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Remeras</t>
+          <t>Jeans</t>
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D75" s="6">
         <f>IF(B75=0, "N/A", (C75-B75)/B75)</f>
@@ -32637,7 +32673,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Sweaters</t>
+          <t>Jogging</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
@@ -32650,115 +32686,109 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Remeras</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D77" s="6">
+        <f>IF(B77=0, "N/A", (C77-B77)/B77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Sweaters</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" s="3" t="n"/>
+      <c r="D78" s="6">
+        <f>IF(B78=0, "N/A", (C78-B78)/B78)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
         <is>
           <t>Totals</t>
         </is>
       </c>
-      <c r="B77" s="4">
-        <f>SUM($B62:$B76)</f>
-        <v/>
-      </c>
-      <c r="C77" s="4">
-        <f>SUM($C62:$C76)</f>
-        <v/>
-      </c>
-      <c r="D77" s="7">
-        <f>IF(B77=0, "N/A", (C77-B77)/B77)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="1" t="inlineStr">
+      <c r="B79" s="4">
+        <f>SUM($B64:$B78)</f>
+        <v/>
+      </c>
+      <c r="C79" s="4">
+        <f>SUM($C64:$C78)</f>
+        <v/>
+      </c>
+      <c r="D79" s="7">
+        <f>IF(B79=0, "N/A", (C79-B79)/B79)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
         <is>
           <t>Sales Amount from August 01, 2026 to August 12, 2026</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="1" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
         <is>
           <t>Familias</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
+      <c r="B83" s="1" t="inlineStr">
         <is>
           <t>LIBERT.R</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>PASO.R</t>
         </is>
       </c>
-      <c r="D81" s="1" t="inlineStr">
+      <c r="D83" s="1" t="inlineStr">
         <is>
           <t>P.OESTE</t>
         </is>
       </c>
-      <c r="E81" s="1" t="inlineStr">
+      <c r="E83" s="1" t="inlineStr">
         <is>
           <t>VIRREYES</t>
         </is>
       </c>
-      <c r="F81" s="1" t="inlineStr">
+      <c r="F83" s="1" t="inlineStr">
         <is>
           <t>Totals</t>
         </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>Accesorios</t>
-        </is>
-      </c>
-      <c r="B82" s="8" t="n">
-        <v>68900</v>
-      </c>
-      <c r="C82" s="8" t="n">
-        <v>231231.6664</v>
-      </c>
-      <c r="D82" s="8" t="n">
-        <v>727780.0012000001</v>
-      </c>
-      <c r="E82" s="8" t="n"/>
-      <c r="F82" s="9">
-        <f>B82+C82+D82+E82</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>Bermudas</t>
-        </is>
-      </c>
-      <c r="B83" s="8" t="n"/>
-      <c r="C83" s="8" t="n">
-        <v>59800</v>
-      </c>
-      <c r="D83" s="8" t="n"/>
-      <c r="E83" s="8" t="n"/>
-      <c r="F83" s="9">
-        <f>B83+C83+D83+E83</f>
-        <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Boxer</t>
+          <t>Accesorios</t>
         </is>
       </c>
       <c r="B84" s="8" t="n">
-        <v>71537.9969</v>
+        <v>68900</v>
       </c>
       <c r="C84" s="8" t="n">
-        <v>44700</v>
+        <v>231231.6664</v>
       </c>
       <c r="D84" s="8" t="n">
-        <v>283100</v>
+        <v>727780.0012000001</v>
       </c>
       <c r="E84" s="8" t="n"/>
       <c r="F84" s="9">
@@ -32769,21 +32799,15 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Buzo Cuello Redondo</t>
-        </is>
-      </c>
-      <c r="B85" s="8" t="n">
-        <v>1069909.8974</v>
-      </c>
+          <t>Bermudas</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="n"/>
       <c r="C85" s="8" t="n">
-        <v>675191.6217</v>
-      </c>
-      <c r="D85" s="8" t="n">
-        <v>3653415.5412</v>
-      </c>
-      <c r="E85" s="8" t="n">
-        <v>34200</v>
-      </c>
+        <v>59800</v>
+      </c>
+      <c r="D85" s="8" t="n"/>
+      <c r="E85" s="8" t="n"/>
       <c r="F85" s="9">
         <f>B85+C85+D85+E85</f>
         <v/>
@@ -32792,13 +32816,17 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Buzos</t>
-        </is>
-      </c>
-      <c r="B86" s="8" t="n"/>
-      <c r="C86" s="8" t="n"/>
+          <t>Boxer</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="n">
+        <v>71537.9969</v>
+      </c>
+      <c r="C86" s="8" t="n">
+        <v>44700</v>
+      </c>
       <c r="D86" s="8" t="n">
-        <v>223600</v>
+        <v>283100</v>
       </c>
       <c r="E86" s="8" t="n"/>
       <c r="F86" s="9">
@@ -32809,17 +32837,13 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Capucha</t>
-        </is>
-      </c>
-      <c r="B87" s="8" t="n">
-        <v>686298.818</v>
-      </c>
-      <c r="C87" s="8" t="n">
-        <v>394010</v>
-      </c>
+          <t>Buzo C Capucha Rustico</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="n"/>
+      <c r="C87" s="8" t="n"/>
       <c r="D87" s="8" t="n">
-        <v>1637810</v>
+        <v>129800</v>
       </c>
       <c r="E87" s="8" t="n"/>
       <c r="F87" s="9">
@@ -32830,20 +32854,20 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Capucha Orangutan</t>
+          <t>Buzo Cuello Redondo</t>
         </is>
       </c>
       <c r="B88" s="8" t="n">
-        <v>100530.0681</v>
+        <v>1069909.8974</v>
       </c>
       <c r="C88" s="8" t="n">
-        <v>156224.2602</v>
+        <v>675191.6217</v>
       </c>
       <c r="D88" s="8" t="n">
-        <v>1639729</v>
+        <v>3653415.5412</v>
       </c>
       <c r="E88" s="8" t="n">
-        <v>184629.9998</v>
+        <v>34200</v>
       </c>
       <c r="F88" s="9">
         <f>B88+C88+D88+E88</f>
@@ -32853,21 +32877,19 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Redondo Orangutan</t>
+          <t>Buzos C Capucha</t>
         </is>
       </c>
       <c r="B89" s="8" t="n">
-        <v>39900</v>
+        <v>686298.818</v>
       </c>
       <c r="C89" s="8" t="n">
-        <v>35910</v>
+        <v>394010</v>
       </c>
       <c r="D89" s="8" t="n">
-        <v>119700</v>
-      </c>
-      <c r="E89" s="8" t="n">
-        <v>77800</v>
-      </c>
+        <v>1508010</v>
+      </c>
+      <c r="E89" s="8" t="n"/>
       <c r="F89" s="9">
         <f>B89+C89+D89+E89</f>
         <v/>
@@ -32876,15 +32898,21 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Buzos Medio Cierre</t>
-        </is>
-      </c>
-      <c r="B90" s="8" t="n"/>
-      <c r="C90" s="8" t="n"/>
+          <t>Buzos C Capucha Orangutan</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="n">
+        <v>100530.0681</v>
+      </c>
+      <c r="C90" s="8" t="n">
+        <v>156224.2602</v>
+      </c>
       <c r="D90" s="8" t="n">
-        <v>49000</v>
-      </c>
-      <c r="E90" s="8" t="n"/>
+        <v>1639729</v>
+      </c>
+      <c r="E90" s="8" t="n">
+        <v>184629.9998</v>
+      </c>
       <c r="F90" s="9">
         <f>B90+C90+D90+E90</f>
         <v/>
@@ -32893,15 +32921,21 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Calzado</t>
-        </is>
-      </c>
-      <c r="B91" s="8" t="n"/>
-      <c r="C91" s="8" t="n"/>
+          <t>Buzos C Redondo Orangutan</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="n">
+        <v>39900</v>
+      </c>
+      <c r="C91" s="8" t="n">
+        <v>35910</v>
+      </c>
       <c r="D91" s="8" t="n">
-        <v>39000</v>
-      </c>
-      <c r="E91" s="8" t="n"/>
+        <v>119700</v>
+      </c>
+      <c r="E91" s="8" t="n">
+        <v>77800</v>
+      </c>
       <c r="F91" s="9">
         <f>B91+C91+D91+E91</f>
         <v/>
@@ -32910,16 +32944,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Camisas</t>
-        </is>
-      </c>
-      <c r="B92" s="8" t="n">
-        <v>204000</v>
-      </c>
-      <c r="C92" s="8" t="n">
-        <v>101750</v>
-      </c>
-      <c r="D92" s="8" t="n"/>
+          <t>Buzos C Redondo Rustico</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="n"/>
+      <c r="C92" s="8" t="n"/>
+      <c r="D92" s="8" t="n">
+        <v>223600</v>
+      </c>
       <c r="E92" s="8" t="n"/>
       <c r="F92" s="9">
         <f>B92+C92+D92+E92</f>
@@ -32929,17 +32961,13 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Camisetas Manga Larga</t>
-        </is>
-      </c>
-      <c r="B93" s="8" t="n">
-        <v>243100</v>
-      </c>
-      <c r="C93" s="8" t="n">
-        <v>322686.7454</v>
-      </c>
+          <t>Buzos Medio Cierre</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="n"/>
+      <c r="C93" s="8" t="n"/>
       <c r="D93" s="8" t="n">
-        <v>73900</v>
+        <v>49000</v>
       </c>
       <c r="E93" s="8" t="n"/>
       <c r="F93" s="9">
@@ -32950,17 +32978,13 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Camisetas Manga Larga Orangutan</t>
-        </is>
-      </c>
-      <c r="B94" s="8" t="n">
-        <v>51800</v>
-      </c>
-      <c r="C94" s="8" t="n">
-        <v>50587.86990000001</v>
-      </c>
+          <t>Calzado</t>
+        </is>
+      </c>
+      <c r="B94" s="8" t="n"/>
+      <c r="C94" s="8" t="n"/>
       <c r="D94" s="8" t="n">
-        <v>330706.4352</v>
+        <v>39000</v>
       </c>
       <c r="E94" s="8" t="n"/>
       <c r="F94" s="9">
@@ -32971,16 +32995,16 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Campera S Capucha</t>
+          <t>Camisas</t>
         </is>
       </c>
       <c r="B95" s="8" t="n">
-        <v>79000</v>
-      </c>
-      <c r="C95" s="8" t="n"/>
-      <c r="D95" s="8" t="n">
-        <v>147000</v>
-      </c>
+        <v>204000</v>
+      </c>
+      <c r="C95" s="8" t="n">
+        <v>101750</v>
+      </c>
+      <c r="D95" s="8" t="n"/>
       <c r="E95" s="8" t="n"/>
       <c r="F95" s="9">
         <f>B95+C95+D95+E95</f>
@@ -32990,17 +33014,17 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Camperas Capucha</t>
+          <t>Camisetas Manga Larga</t>
         </is>
       </c>
       <c r="B96" s="8" t="n">
-        <v>242700</v>
+        <v>243100</v>
       </c>
       <c r="C96" s="8" t="n">
-        <v>357777.3243</v>
+        <v>322686.7454</v>
       </c>
       <c r="D96" s="8" t="n">
-        <v>1818094.4589</v>
+        <v>73900</v>
       </c>
       <c r="E96" s="8" t="n"/>
       <c r="F96" s="9">
@@ -33011,15 +33035,17 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Camperas De Abrigo</t>
+          <t>Camisetas Manga Larga Orangutan</t>
         </is>
       </c>
       <c r="B97" s="8" t="n">
-        <v>119800</v>
-      </c>
-      <c r="C97" s="8" t="n"/>
+        <v>51800</v>
+      </c>
+      <c r="C97" s="8" t="n">
+        <v>50587.86990000001</v>
+      </c>
       <c r="D97" s="8" t="n">
-        <v>631200</v>
+        <v>330706.4352</v>
       </c>
       <c r="E97" s="8" t="n"/>
       <c r="F97" s="9">
@@ -33030,17 +33056,15 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Chombas</t>
+          <t>Campera S Capucha</t>
         </is>
       </c>
       <c r="B98" s="8" t="n">
-        <v>114350</v>
-      </c>
-      <c r="C98" s="8" t="n">
-        <v>21900</v>
-      </c>
+        <v>79000</v>
+      </c>
+      <c r="C98" s="8" t="n"/>
       <c r="D98" s="8" t="n">
-        <v>87210</v>
+        <v>147000</v>
       </c>
       <c r="E98" s="8" t="n"/>
       <c r="F98" s="9">
@@ -33051,16 +33075,18 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Chombas Manga Larga</t>
+          <t>Camperas Capucha</t>
         </is>
       </c>
       <c r="B99" s="8" t="n">
-        <v>35900</v>
+        <v>242700</v>
       </c>
       <c r="C99" s="8" t="n">
-        <v>107700</v>
-      </c>
-      <c r="D99" s="8" t="n"/>
+        <v>357777.3243</v>
+      </c>
+      <c r="D99" s="8" t="n">
+        <v>1818094.4589</v>
+      </c>
       <c r="E99" s="8" t="n"/>
       <c r="F99" s="9">
         <f>B99+C99+D99+E99</f>
@@ -33070,15 +33096,17 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Detroit</t>
-        </is>
-      </c>
-      <c r="B100" s="8" t="n"/>
+          <t>Camperas De Abrigo</t>
+        </is>
+      </c>
+      <c r="B100" s="8" t="n">
+        <v>119800</v>
+      </c>
       <c r="C100" s="8" t="n"/>
-      <c r="D100" s="8" t="n"/>
-      <c r="E100" s="8" t="n">
-        <v>31410</v>
-      </c>
+      <c r="D100" s="8" t="n">
+        <v>631200</v>
+      </c>
+      <c r="E100" s="8" t="n"/>
       <c r="F100" s="9">
         <f>B100+C100+D100+E100</f>
         <v/>
@@ -33087,21 +33115,19 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Jeans</t>
+          <t>Chombas</t>
         </is>
       </c>
       <c r="B101" s="8" t="n">
-        <v>1160072.0382</v>
+        <v>114350</v>
       </c>
       <c r="C101" s="8" t="n">
-        <v>1248229.9203</v>
+        <v>21900</v>
       </c>
       <c r="D101" s="8" t="n">
-        <v>10077844.5648</v>
-      </c>
-      <c r="E101" s="8" t="n">
-        <v>143382</v>
-      </c>
+        <v>87210</v>
+      </c>
+      <c r="E101" s="8" t="n"/>
       <c r="F101" s="9">
         <f>B101+C101+D101+E101</f>
         <v/>
@@ -33110,16 +33136,16 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Jogging</t>
-        </is>
-      </c>
-      <c r="B102" s="8" t="n"/>
+          <t>Chombas Manga Larga</t>
+        </is>
+      </c>
+      <c r="B102" s="8" t="n">
+        <v>35900</v>
+      </c>
       <c r="C102" s="8" t="n">
-        <v>99500</v>
-      </c>
-      <c r="D102" s="8" t="n">
-        <v>340150.0015</v>
-      </c>
+        <v>107700</v>
+      </c>
+      <c r="D102" s="8" t="n"/>
       <c r="E102" s="8" t="n"/>
       <c r="F102" s="9">
         <f>B102+C102+D102+E102</f>
@@ -33129,20 +33155,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Remeras</t>
-        </is>
-      </c>
-      <c r="B103" s="8" t="n">
-        <v>235821.1814</v>
-      </c>
-      <c r="C103" s="8" t="n">
-        <v>1262224.5918</v>
-      </c>
-      <c r="D103" s="8" t="n">
-        <v>3595324.9972</v>
-      </c>
+          <t>Detroit</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="n"/>
+      <c r="C103" s="8" t="n"/>
+      <c r="D103" s="8" t="n"/>
       <c r="E103" s="8" t="n">
-        <v>50310.00019999999</v>
+        <v>31410</v>
       </c>
       <c r="F103" s="9">
         <f>B103+C103+D103+E103</f>
@@ -33152,305 +33172,235 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Sweaters</t>
+          <t>Jeans</t>
         </is>
       </c>
       <c r="B104" s="8" t="n">
-        <v>132800</v>
+        <v>1160072.0382</v>
       </c>
       <c r="C104" s="8" t="n">
-        <v>91980</v>
+        <v>1248229.9203</v>
       </c>
       <c r="D104" s="8" t="n">
-        <v>79000</v>
-      </c>
-      <c r="E104" s="8" t="n"/>
+        <v>10077844.5648</v>
+      </c>
+      <c r="E104" s="8" t="n">
+        <v>143382</v>
+      </c>
       <c r="F104" s="9">
         <f>B104+C104+D104+E104</f>
         <v/>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="5" t="inlineStr">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Jogging</t>
+        </is>
+      </c>
+      <c r="B105" s="8" t="n"/>
+      <c r="C105" s="8" t="n">
+        <v>99500</v>
+      </c>
+      <c r="D105" s="8" t="n">
+        <v>340150.0015</v>
+      </c>
+      <c r="E105" s="8" t="n"/>
+      <c r="F105" s="9">
+        <f>B105+C105+D105+E105</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Remeras</t>
+        </is>
+      </c>
+      <c r="B106" s="8" t="n">
+        <v>235821.1814</v>
+      </c>
+      <c r="C106" s="8" t="n">
+        <v>1262224.5918</v>
+      </c>
+      <c r="D106" s="8" t="n">
+        <v>3595324.9972</v>
+      </c>
+      <c r="E106" s="8" t="n">
+        <v>50310.00019999999</v>
+      </c>
+      <c r="F106" s="9">
+        <f>B106+C106+D106+E106</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Sweaters</t>
+        </is>
+      </c>
+      <c r="B107" s="8" t="n">
+        <v>132800</v>
+      </c>
+      <c r="C107" s="8" t="n">
+        <v>91980</v>
+      </c>
+      <c r="D107" s="8" t="n">
+        <v>79000</v>
+      </c>
+      <c r="E107" s="8" t="n"/>
+      <c r="F107" s="9">
+        <f>B107+C107+D107+E107</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
         <is>
           <t>Totals</t>
         </is>
       </c>
-      <c r="B105" s="9">
-        <f>SUM($B$82:$B$104)</f>
-        <v/>
-      </c>
-      <c r="C105" s="9">
-        <f>SUM($C$82:$C$104)</f>
-        <v/>
-      </c>
-      <c r="D105" s="9">
-        <f>SUM($D$82:$D$104)</f>
-        <v/>
-      </c>
-      <c r="E105" s="9">
-        <f>SUM($E$82:$E$104)</f>
-        <v/>
-      </c>
-      <c r="F105" s="9">
-        <f>SUM($F$82:$F$104)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="1" t="inlineStr">
+      <c r="B108" s="9">
+        <f>SUM($B$84:$B$107)</f>
+        <v/>
+      </c>
+      <c r="C108" s="9">
+        <f>SUM($C$84:$C$107)</f>
+        <v/>
+      </c>
+      <c r="D108" s="9">
+        <f>SUM($D$84:$D$107)</f>
+        <v/>
+      </c>
+      <c r="E108" s="9">
+        <f>SUM($E$84:$E$107)</f>
+        <v/>
+      </c>
+      <c r="F108" s="9">
+        <f>SUM($F$84:$F$107)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
         <is>
           <t>YoY Sales Amount Comparison - Branch Group 1</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="B109" s="1" t="inlineStr">
+    <row r="112">
+      <c r="B112" s="1" t="inlineStr">
         <is>
           <t>LIBERT.R</t>
         </is>
       </c>
-      <c r="C109" s="1" t="n"/>
-      <c r="D109" s="1" t="n"/>
-      <c r="E109" s="1" t="inlineStr">
+      <c r="C112" s="1" t="n"/>
+      <c r="D112" s="1" t="n"/>
+      <c r="E112" s="1" t="inlineStr">
         <is>
           <t>PASO.R</t>
         </is>
       </c>
-      <c r="F109" s="1" t="n"/>
-      <c r="G109" s="1" t="n"/>
-      <c r="H109" s="1" t="inlineStr">
+      <c r="F112" s="1" t="n"/>
+      <c r="G112" s="1" t="n"/>
+      <c r="H112" s="1" t="inlineStr">
         <is>
           <t>P.OESTE</t>
         </is>
       </c>
-      <c r="I109" s="1" t="n"/>
-      <c r="J109" s="1" t="n"/>
-      <c r="K109" s="1" t="inlineStr">
+      <c r="I112" s="1" t="n"/>
+      <c r="J112" s="1" t="n"/>
+      <c r="K112" s="1" t="inlineStr">
         <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="L109" s="1" t="n"/>
-      <c r="M109" s="1" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="1" t="inlineStr">
+      <c r="L112" s="1" t="n"/>
+      <c r="M112" s="1" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
         <is>
           <t>Familias</t>
         </is>
       </c>
-      <c r="B110" s="1" t="n">
+      <c r="B113" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="C110" s="1" t="n">
+      <c r="C113" s="1" t="n">
         <v>2026</v>
       </c>
-      <c r="D110" s="1" t="inlineStr">
+      <c r="D113" s="1" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E110" s="1" t="n">
+      <c r="E113" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="F110" s="1" t="n">
+      <c r="F113" s="1" t="n">
         <v>2026</v>
       </c>
-      <c r="G110" s="1" t="inlineStr">
+      <c r="G113" s="1" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H110" s="1" t="n">
+      <c r="H113" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="I110" s="1" t="n">
+      <c r="I113" s="1" t="n">
         <v>2026</v>
       </c>
-      <c r="J110" s="1" t="inlineStr">
+      <c r="J113" s="1" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="K110" s="1" t="n">
+      <c r="K113" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="L110" s="1" t="n">
+      <c r="L113" s="1" t="n">
         <v>2026</v>
       </c>
-      <c r="M110" s="1" t="inlineStr">
+      <c r="M113" s="1" t="inlineStr">
         <is>
           <t>%</t>
         </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>Accesorios</t>
-        </is>
-      </c>
-      <c r="B111" s="8" t="n">
-        <v>87750</v>
-      </c>
-      <c r="C111" s="8" t="n">
-        <v>68900</v>
-      </c>
-      <c r="D111" s="6">
-        <f>IF(B111=0, "N/A", (C111-B111)/B111)</f>
-        <v/>
-      </c>
-      <c r="E111" s="8" t="n">
-        <v>18000</v>
-      </c>
-      <c r="F111" s="8" t="n">
-        <v>231231.6664</v>
-      </c>
-      <c r="G111" s="6">
-        <f>IF(E111=0, "N/A", (F111-E111)/E111)</f>
-        <v/>
-      </c>
-      <c r="H111" s="8" t="n">
-        <v>535509.352</v>
-      </c>
-      <c r="I111" s="8" t="n">
-        <v>727780.0012000001</v>
-      </c>
-      <c r="J111" s="6">
-        <f>IF(H111=0, "N/A", (I111-H111)/H111)</f>
-        <v/>
-      </c>
-      <c r="K111" s="8">
-        <f>B111+E111+H111</f>
-        <v/>
-      </c>
-      <c r="L111" s="8">
-        <f>C111+F111+I111</f>
-        <v/>
-      </c>
-      <c r="M111" s="6">
-        <f>IF(K111=0, "N/A", (L111-K111)/K111)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>Bermudas</t>
-        </is>
-      </c>
-      <c r="B112" s="8" t="n"/>
-      <c r="C112" s="8" t="n"/>
-      <c r="D112" s="6">
-        <f>IF(B112=0, "N/A", (C112-B112)/B112)</f>
-        <v/>
-      </c>
-      <c r="E112" s="8" t="n"/>
-      <c r="F112" s="8" t="n">
-        <v>59800</v>
-      </c>
-      <c r="G112" s="6">
-        <f>IF(E112=0, "N/A", (F112-E112)/E112)</f>
-        <v/>
-      </c>
-      <c r="H112" s="8" t="n"/>
-      <c r="I112" s="8" t="n"/>
-      <c r="J112" s="6">
-        <f>IF(H112=0, "N/A", (I112-H112)/H112)</f>
-        <v/>
-      </c>
-      <c r="K112" s="8">
-        <f>B112+E112+H112</f>
-        <v/>
-      </c>
-      <c r="L112" s="8">
-        <f>C112+F112+I112</f>
-        <v/>
-      </c>
-      <c r="M112" s="6">
-        <f>IF(K112=0, "N/A", (L112-K112)/K112)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>Boxer</t>
-        </is>
-      </c>
-      <c r="B113" s="8" t="n">
-        <v>55000</v>
-      </c>
-      <c r="C113" s="8" t="n">
-        <v>71537.9969</v>
-      </c>
-      <c r="D113" s="6">
-        <f>IF(B113=0, "N/A", (C113-B113)/B113)</f>
-        <v/>
-      </c>
-      <c r="E113" s="8" t="n"/>
-      <c r="F113" s="8" t="n">
-        <v>44700</v>
-      </c>
-      <c r="G113" s="6">
-        <f>IF(E113=0, "N/A", (F113-E113)/E113)</f>
-        <v/>
-      </c>
-      <c r="H113" s="8" t="n">
-        <v>251000</v>
-      </c>
-      <c r="I113" s="8" t="n">
-        <v>283100</v>
-      </c>
-      <c r="J113" s="6">
-        <f>IF(H113=0, "N/A", (I113-H113)/H113)</f>
-        <v/>
-      </c>
-      <c r="K113" s="8">
-        <f>B113+E113+H113</f>
-        <v/>
-      </c>
-      <c r="L113" s="8">
-        <f>C113+F113+I113</f>
-        <v/>
-      </c>
-      <c r="M113" s="6">
-        <f>IF(K113=0, "N/A", (L113-K113)/K113)</f>
-        <v/>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Buzo Cuello Redondo</t>
+          <t>Accesorios</t>
         </is>
       </c>
       <c r="B114" s="8" t="n">
-        <v>435800</v>
+        <v>87750</v>
       </c>
       <c r="C114" s="8" t="n">
-        <v>1069909.8974</v>
+        <v>68900</v>
       </c>
       <c r="D114" s="6">
         <f>IF(B114=0, "N/A", (C114-B114)/B114)</f>
         <v/>
       </c>
       <c r="E114" s="8" t="n">
-        <v>1508623.6957</v>
+        <v>18000</v>
       </c>
       <c r="F114" s="8" t="n">
-        <v>675191.6217</v>
+        <v>231231.6664</v>
       </c>
       <c r="G114" s="6">
         <f>IF(E114=0, "N/A", (F114-E114)/E114)</f>
         <v/>
       </c>
       <c r="H114" s="8" t="n">
-        <v>1975755.5941</v>
+        <v>535509.352</v>
       </c>
       <c r="I114" s="8" t="n">
-        <v>3653415.5412</v>
+        <v>727780.0012000001</v>
       </c>
       <c r="J114" s="6">
         <f>IF(H114=0, "N/A", (I114-H114)/H114)</f>
@@ -33472,7 +33422,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Buzos</t>
+          <t>Bermudas</t>
         </is>
       </c>
       <c r="B115" s="8" t="n"/>
@@ -33482,15 +33432,15 @@
         <v/>
       </c>
       <c r="E115" s="8" t="n"/>
-      <c r="F115" s="8" t="n"/>
+      <c r="F115" s="8" t="n">
+        <v>59800</v>
+      </c>
       <c r="G115" s="6">
         <f>IF(E115=0, "N/A", (F115-E115)/E115)</f>
         <v/>
       </c>
       <c r="H115" s="8" t="n"/>
-      <c r="I115" s="8" t="n">
-        <v>223600</v>
-      </c>
+      <c r="I115" s="8" t="n"/>
       <c r="J115" s="6">
         <f>IF(H115=0, "N/A", (I115-H115)/H115)</f>
         <v/>
@@ -33511,34 +33461,32 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Capucha</t>
+          <t>Boxer</t>
         </is>
       </c>
       <c r="B116" s="8" t="n">
-        <v>810608.8548</v>
+        <v>55000</v>
       </c>
       <c r="C116" s="8" t="n">
-        <v>686298.818</v>
+        <v>71537.9969</v>
       </c>
       <c r="D116" s="6">
         <f>IF(B116=0, "N/A", (C116-B116)/B116)</f>
         <v/>
       </c>
-      <c r="E116" s="8" t="n">
-        <v>894898.1248</v>
-      </c>
+      <c r="E116" s="8" t="n"/>
       <c r="F116" s="8" t="n">
-        <v>394010</v>
+        <v>44700</v>
       </c>
       <c r="G116" s="6">
         <f>IF(E116=0, "N/A", (F116-E116)/E116)</f>
         <v/>
       </c>
       <c r="H116" s="8" t="n">
-        <v>2224648.4533</v>
+        <v>251000</v>
       </c>
       <c r="I116" s="8" t="n">
-        <v>1637810</v>
+        <v>283100</v>
       </c>
       <c r="J116" s="6">
         <f>IF(H116=0, "N/A", (I116-H116)/H116)</f>
@@ -33560,28 +33508,24 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Capucha Orangutan</t>
+          <t>Buzo C Capucha Rustico</t>
         </is>
       </c>
       <c r="B117" s="8" t="n"/>
-      <c r="C117" s="8" t="n">
-        <v>100530.0681</v>
-      </c>
+      <c r="C117" s="8" t="n"/>
       <c r="D117" s="6">
         <f>IF(B117=0, "N/A", (C117-B117)/B117)</f>
         <v/>
       </c>
       <c r="E117" s="8" t="n"/>
-      <c r="F117" s="8" t="n">
-        <v>156224.2602</v>
-      </c>
+      <c r="F117" s="8" t="n"/>
       <c r="G117" s="6">
         <f>IF(E117=0, "N/A", (F117-E117)/E117)</f>
         <v/>
       </c>
       <c r="H117" s="8" t="n"/>
       <c r="I117" s="8" t="n">
-        <v>1639729</v>
+        <v>129800</v>
       </c>
       <c r="J117" s="6">
         <f>IF(H117=0, "N/A", (I117-H117)/H117)</f>
@@ -33603,28 +33547,34 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Redondo Orangutan</t>
-        </is>
-      </c>
-      <c r="B118" s="8" t="n"/>
+          <t>Buzo Cuello Redondo</t>
+        </is>
+      </c>
+      <c r="B118" s="8" t="n">
+        <v>435800</v>
+      </c>
       <c r="C118" s="8" t="n">
-        <v>39900</v>
+        <v>1069909.8974</v>
       </c>
       <c r="D118" s="6">
         <f>IF(B118=0, "N/A", (C118-B118)/B118)</f>
         <v/>
       </c>
-      <c r="E118" s="8" t="n"/>
+      <c r="E118" s="8" t="n">
+        <v>1508623.6957</v>
+      </c>
       <c r="F118" s="8" t="n">
-        <v>35910</v>
+        <v>675191.6217</v>
       </c>
       <c r="G118" s="6">
         <f>IF(E118=0, "N/A", (F118-E118)/E118)</f>
         <v/>
       </c>
-      <c r="H118" s="8" t="n"/>
+      <c r="H118" s="8" t="n">
+        <v>1975755.5941</v>
+      </c>
       <c r="I118" s="8" t="n">
-        <v>119700</v>
+        <v>3653415.5412</v>
       </c>
       <c r="J118" s="6">
         <f>IF(H118=0, "N/A", (I118-H118)/H118)</f>
@@ -33646,28 +33596,34 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Buzos Medio Cierre</t>
-        </is>
-      </c>
-      <c r="B119" s="8" t="n"/>
-      <c r="C119" s="8" t="n"/>
+          <t>Buzos C Capucha</t>
+        </is>
+      </c>
+      <c r="B119" s="8" t="n">
+        <v>810608.8548</v>
+      </c>
+      <c r="C119" s="8" t="n">
+        <v>686298.818</v>
+      </c>
       <c r="D119" s="6">
         <f>IF(B119=0, "N/A", (C119-B119)/B119)</f>
         <v/>
       </c>
       <c r="E119" s="8" t="n">
-        <v>77800</v>
-      </c>
-      <c r="F119" s="8" t="n"/>
+        <v>894898.1248</v>
+      </c>
+      <c r="F119" s="8" t="n">
+        <v>394010</v>
+      </c>
       <c r="G119" s="6">
         <f>IF(E119=0, "N/A", (F119-E119)/E119)</f>
         <v/>
       </c>
       <c r="H119" s="8" t="n">
-        <v>-75280</v>
+        <v>2224648.4533</v>
       </c>
       <c r="I119" s="8" t="n">
-        <v>49000</v>
+        <v>1508010</v>
       </c>
       <c r="J119" s="6">
         <f>IF(H119=0, "N/A", (I119-H119)/H119)</f>
@@ -33689,24 +33645,28 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Calzado</t>
+          <t>Buzos C Capucha Orangutan</t>
         </is>
       </c>
       <c r="B120" s="8" t="n"/>
-      <c r="C120" s="8" t="n"/>
+      <c r="C120" s="8" t="n">
+        <v>100530.0681</v>
+      </c>
       <c r="D120" s="6">
         <f>IF(B120=0, "N/A", (C120-B120)/B120)</f>
         <v/>
       </c>
       <c r="E120" s="8" t="n"/>
-      <c r="F120" s="8" t="n"/>
+      <c r="F120" s="8" t="n">
+        <v>156224.2602</v>
+      </c>
       <c r="G120" s="6">
         <f>IF(E120=0, "N/A", (F120-E120)/E120)</f>
         <v/>
       </c>
       <c r="H120" s="8" t="n"/>
       <c r="I120" s="8" t="n">
-        <v>39000</v>
+        <v>1639729</v>
       </c>
       <c r="J120" s="6">
         <f>IF(H120=0, "N/A", (I120-H120)/H120)</f>
@@ -33728,33 +33688,29 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Camisas</t>
-        </is>
-      </c>
-      <c r="B121" s="8" t="n">
-        <v>166050</v>
-      </c>
+          <t>Buzos C Redondo Orangutan</t>
+        </is>
+      </c>
+      <c r="B121" s="8" t="n"/>
       <c r="C121" s="8" t="n">
-        <v>204000</v>
+        <v>39900</v>
       </c>
       <c r="D121" s="6">
         <f>IF(B121=0, "N/A", (C121-B121)/B121)</f>
         <v/>
       </c>
-      <c r="E121" s="8" t="n">
-        <v>59900</v>
-      </c>
+      <c r="E121" s="8" t="n"/>
       <c r="F121" s="8" t="n">
-        <v>101750</v>
+        <v>35910</v>
       </c>
       <c r="G121" s="6">
         <f>IF(E121=0, "N/A", (F121-E121)/E121)</f>
         <v/>
       </c>
-      <c r="H121" s="8" t="n">
-        <v>619296.6097</v>
-      </c>
-      <c r="I121" s="8" t="n"/>
+      <c r="H121" s="8" t="n"/>
+      <c r="I121" s="8" t="n">
+        <v>119700</v>
+      </c>
       <c r="J121" s="6">
         <f>IF(H121=0, "N/A", (I121-H121)/H121)</f>
         <v/>
@@ -33775,34 +33731,24 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Camisetas Manga Larga</t>
-        </is>
-      </c>
-      <c r="B122" s="8" t="n">
-        <v>222010</v>
-      </c>
-      <c r="C122" s="8" t="n">
-        <v>243100</v>
-      </c>
+          <t>Buzos C Redondo Rustico</t>
+        </is>
+      </c>
+      <c r="B122" s="8" t="n"/>
+      <c r="C122" s="8" t="n"/>
       <c r="D122" s="6">
         <f>IF(B122=0, "N/A", (C122-B122)/B122)</f>
         <v/>
       </c>
-      <c r="E122" s="8" t="n">
-        <v>79742.6686</v>
-      </c>
-      <c r="F122" s="8" t="n">
-        <v>322686.7454</v>
-      </c>
+      <c r="E122" s="8" t="n"/>
+      <c r="F122" s="8" t="n"/>
       <c r="G122" s="6">
         <f>IF(E122=0, "N/A", (F122-E122)/E122)</f>
         <v/>
       </c>
-      <c r="H122" s="8" t="n">
-        <v>258645.9664</v>
-      </c>
+      <c r="H122" s="8" t="n"/>
       <c r="I122" s="8" t="n">
-        <v>73900</v>
+        <v>223600</v>
       </c>
       <c r="J122" s="6">
         <f>IF(H122=0, "N/A", (I122-H122)/H122)</f>
@@ -33824,28 +33770,28 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Camisetas Manga Larga Orangutan</t>
+          <t>Buzos Medio Cierre</t>
         </is>
       </c>
       <c r="B123" s="8" t="n"/>
-      <c r="C123" s="8" t="n">
-        <v>51800</v>
-      </c>
+      <c r="C123" s="8" t="n"/>
       <c r="D123" s="6">
         <f>IF(B123=0, "N/A", (C123-B123)/B123)</f>
         <v/>
       </c>
-      <c r="E123" s="8" t="n"/>
-      <c r="F123" s="8" t="n">
-        <v>50587.86990000001</v>
-      </c>
+      <c r="E123" s="8" t="n">
+        <v>77800</v>
+      </c>
+      <c r="F123" s="8" t="n"/>
       <c r="G123" s="6">
         <f>IF(E123=0, "N/A", (F123-E123)/E123)</f>
         <v/>
       </c>
-      <c r="H123" s="8" t="n"/>
+      <c r="H123" s="8" t="n">
+        <v>-75280</v>
+      </c>
       <c r="I123" s="8" t="n">
-        <v>330706.4352</v>
+        <v>49000</v>
       </c>
       <c r="J123" s="6">
         <f>IF(H123=0, "N/A", (I123-H123)/H123)</f>
@@ -33867,32 +33813,24 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Campera S Capucha</t>
-        </is>
-      </c>
-      <c r="B124" s="8" t="n">
-        <v>209400</v>
-      </c>
-      <c r="C124" s="8" t="n">
-        <v>79000</v>
-      </c>
+          <t>Calzado</t>
+        </is>
+      </c>
+      <c r="B124" s="8" t="n"/>
+      <c r="C124" s="8" t="n"/>
       <c r="D124" s="6">
         <f>IF(B124=0, "N/A", (C124-B124)/B124)</f>
         <v/>
       </c>
-      <c r="E124" s="8" t="n">
-        <v>39900</v>
-      </c>
+      <c r="E124" s="8" t="n"/>
       <c r="F124" s="8" t="n"/>
       <c r="G124" s="6">
         <f>IF(E124=0, "N/A", (F124-E124)/E124)</f>
         <v/>
       </c>
-      <c r="H124" s="8" t="n">
-        <v>608202.357</v>
-      </c>
+      <c r="H124" s="8" t="n"/>
       <c r="I124" s="8" t="n">
-        <v>147000</v>
+        <v>39000</v>
       </c>
       <c r="J124" s="6">
         <f>IF(H124=0, "N/A", (I124-H124)/H124)</f>
@@ -33914,35 +33852,33 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Camperas Capucha</t>
+          <t>Camisas</t>
         </is>
       </c>
       <c r="B125" s="8" t="n">
-        <v>79800</v>
+        <v>166050</v>
       </c>
       <c r="C125" s="8" t="n">
-        <v>242700</v>
+        <v>204000</v>
       </c>
       <c r="D125" s="6">
         <f>IF(B125=0, "N/A", (C125-B125)/B125)</f>
         <v/>
       </c>
       <c r="E125" s="8" t="n">
-        <v>-38900</v>
+        <v>59900</v>
       </c>
       <c r="F125" s="8" t="n">
-        <v>357777.3243</v>
+        <v>101750</v>
       </c>
       <c r="G125" s="6">
         <f>IF(E125=0, "N/A", (F125-E125)/E125)</f>
         <v/>
       </c>
       <c r="H125" s="8" t="n">
-        <v>876520</v>
-      </c>
-      <c r="I125" s="8" t="n">
-        <v>1818094.4589</v>
-      </c>
+        <v>619296.6097</v>
+      </c>
+      <c r="I125" s="8" t="n"/>
       <c r="J125" s="6">
         <f>IF(H125=0, "N/A", (I125-H125)/H125)</f>
         <v/>
@@ -33963,32 +33899,34 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Camperas De Abrigo</t>
+          <t>Camisetas Manga Larga</t>
         </is>
       </c>
       <c r="B126" s="8" t="n">
-        <v>724740</v>
+        <v>222010</v>
       </c>
       <c r="C126" s="8" t="n">
-        <v>119800</v>
+        <v>243100</v>
       </c>
       <c r="D126" s="6">
         <f>IF(B126=0, "N/A", (C126-B126)/B126)</f>
         <v/>
       </c>
       <c r="E126" s="8" t="n">
-        <v>279600</v>
-      </c>
-      <c r="F126" s="8" t="n"/>
+        <v>79742.6686</v>
+      </c>
+      <c r="F126" s="8" t="n">
+        <v>322686.7454</v>
+      </c>
       <c r="G126" s="6">
         <f>IF(E126=0, "N/A", (F126-E126)/E126)</f>
         <v/>
       </c>
       <c r="H126" s="8" t="n">
-        <v>746800</v>
+        <v>258645.9664</v>
       </c>
       <c r="I126" s="8" t="n">
-        <v>631200</v>
+        <v>73900</v>
       </c>
       <c r="J126" s="6">
         <f>IF(H126=0, "N/A", (I126-H126)/H126)</f>
@@ -34010,34 +33948,28 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Chombas</t>
-        </is>
-      </c>
-      <c r="B127" s="8" t="n">
-        <v>306929.9116</v>
-      </c>
+          <t>Camisetas Manga Larga Orangutan</t>
+        </is>
+      </c>
+      <c r="B127" s="8" t="n"/>
       <c r="C127" s="8" t="n">
-        <v>114350</v>
+        <v>51800</v>
       </c>
       <c r="D127" s="6">
         <f>IF(B127=0, "N/A", (C127-B127)/B127)</f>
         <v/>
       </c>
-      <c r="E127" s="8" t="n">
-        <v>298900</v>
-      </c>
+      <c r="E127" s="8" t="n"/>
       <c r="F127" s="8" t="n">
-        <v>21900</v>
+        <v>50587.86990000001</v>
       </c>
       <c r="G127" s="6">
         <f>IF(E127=0, "N/A", (F127-E127)/E127)</f>
         <v/>
       </c>
-      <c r="H127" s="8" t="n">
-        <v>130800</v>
-      </c>
+      <c r="H127" s="8" t="n"/>
       <c r="I127" s="8" t="n">
-        <v>87210</v>
+        <v>330706.4352</v>
       </c>
       <c r="J127" s="6">
         <f>IF(H127=0, "N/A", (I127-H127)/H127)</f>
@@ -34059,27 +33991,33 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Chombas Manga Larga</t>
-        </is>
-      </c>
-      <c r="B128" s="8" t="n"/>
+          <t>Campera S Capucha</t>
+        </is>
+      </c>
+      <c r="B128" s="8" t="n">
+        <v>209400</v>
+      </c>
       <c r="C128" s="8" t="n">
-        <v>35900</v>
+        <v>79000</v>
       </c>
       <c r="D128" s="6">
         <f>IF(B128=0, "N/A", (C128-B128)/B128)</f>
         <v/>
       </c>
-      <c r="E128" s="8" t="n"/>
-      <c r="F128" s="8" t="n">
-        <v>107700</v>
-      </c>
+      <c r="E128" s="8" t="n">
+        <v>39900</v>
+      </c>
+      <c r="F128" s="8" t="n"/>
       <c r="G128" s="6">
         <f>IF(E128=0, "N/A", (F128-E128)/E128)</f>
         <v/>
       </c>
-      <c r="H128" s="8" t="n"/>
-      <c r="I128" s="8" t="n"/>
+      <c r="H128" s="8" t="n">
+        <v>608202.357</v>
+      </c>
+      <c r="I128" s="8" t="n">
+        <v>147000</v>
+      </c>
       <c r="J128" s="6">
         <f>IF(H128=0, "N/A", (I128-H128)/H128)</f>
         <v/>
@@ -34100,34 +34038,34 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Jeans</t>
+          <t>Camperas Capucha</t>
         </is>
       </c>
       <c r="B129" s="8" t="n">
-        <v>1861652.3996</v>
+        <v>79800</v>
       </c>
       <c r="C129" s="8" t="n">
-        <v>1160072.0382</v>
+        <v>242700</v>
       </c>
       <c r="D129" s="6">
         <f>IF(B129=0, "N/A", (C129-B129)/B129)</f>
         <v/>
       </c>
       <c r="E129" s="8" t="n">
-        <v>664657.3393999999</v>
+        <v>-38900</v>
       </c>
       <c r="F129" s="8" t="n">
-        <v>1248229.9203</v>
+        <v>357777.3243</v>
       </c>
       <c r="G129" s="6">
         <f>IF(E129=0, "N/A", (F129-E129)/E129)</f>
         <v/>
       </c>
       <c r="H129" s="8" t="n">
-        <v>6401548.4722</v>
+        <v>876520</v>
       </c>
       <c r="I129" s="8" t="n">
-        <v>10077844.5648</v>
+        <v>1818094.4589</v>
       </c>
       <c r="J129" s="6">
         <f>IF(H129=0, "N/A", (I129-H129)/H129)</f>
@@ -34149,32 +34087,32 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Jogging</t>
+          <t>Camperas De Abrigo</t>
         </is>
       </c>
       <c r="B130" s="8" t="n">
-        <v>88500</v>
-      </c>
-      <c r="C130" s="8" t="n"/>
+        <v>724740</v>
+      </c>
+      <c r="C130" s="8" t="n">
+        <v>119800</v>
+      </c>
       <c r="D130" s="6">
         <f>IF(B130=0, "N/A", (C130-B130)/B130)</f>
         <v/>
       </c>
       <c r="E130" s="8" t="n">
-        <v>91986.2179</v>
-      </c>
-      <c r="F130" s="8" t="n">
-        <v>99500</v>
-      </c>
+        <v>279600</v>
+      </c>
+      <c r="F130" s="8" t="n"/>
       <c r="G130" s="6">
         <f>IF(E130=0, "N/A", (F130-E130)/E130)</f>
         <v/>
       </c>
       <c r="H130" s="8" t="n">
-        <v>133440</v>
+        <v>746800</v>
       </c>
       <c r="I130" s="8" t="n">
-        <v>340150.0015</v>
+        <v>631200</v>
       </c>
       <c r="J130" s="6">
         <f>IF(H130=0, "N/A", (I130-H130)/H130)</f>
@@ -34196,27 +34134,35 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Chombas</t>
         </is>
       </c>
       <c r="B131" s="8" t="n">
-        <v>11000</v>
-      </c>
-      <c r="C131" s="8" t="n"/>
+        <v>306929.9116</v>
+      </c>
+      <c r="C131" s="8" t="n">
+        <v>114350</v>
+      </c>
       <c r="D131" s="6">
         <f>IF(B131=0, "N/A", (C131-B131)/B131)</f>
         <v/>
       </c>
       <c r="E131" s="8" t="n">
-        <v>11000</v>
-      </c>
-      <c r="F131" s="8" t="n"/>
+        <v>298900</v>
+      </c>
+      <c r="F131" s="8" t="n">
+        <v>21900</v>
+      </c>
       <c r="G131" s="6">
         <f>IF(E131=0, "N/A", (F131-E131)/E131)</f>
         <v/>
       </c>
-      <c r="H131" s="8" t="n"/>
-      <c r="I131" s="8" t="n"/>
+      <c r="H131" s="8" t="n">
+        <v>130800</v>
+      </c>
+      <c r="I131" s="8" t="n">
+        <v>87210</v>
+      </c>
       <c r="J131" s="6">
         <f>IF(H131=0, "N/A", (I131-H131)/H131)</f>
         <v/>
@@ -34237,35 +34183,27 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Remeras</t>
-        </is>
-      </c>
-      <c r="B132" s="8" t="n">
-        <v>639866.334</v>
-      </c>
+          <t>Chombas Manga Larga</t>
+        </is>
+      </c>
+      <c r="B132" s="8" t="n"/>
       <c r="C132" s="8" t="n">
-        <v>235821.1814</v>
+        <v>35900</v>
       </c>
       <c r="D132" s="6">
         <f>IF(B132=0, "N/A", (C132-B132)/B132)</f>
         <v/>
       </c>
-      <c r="E132" s="8" t="n">
-        <v>701041.9536</v>
-      </c>
+      <c r="E132" s="8" t="n"/>
       <c r="F132" s="8" t="n">
-        <v>1262224.5918</v>
+        <v>107700</v>
       </c>
       <c r="G132" s="6">
         <f>IF(E132=0, "N/A", (F132-E132)/E132)</f>
         <v/>
       </c>
-      <c r="H132" s="8" t="n">
-        <v>3989267.1953</v>
-      </c>
-      <c r="I132" s="8" t="n">
-        <v>3595324.9972</v>
-      </c>
+      <c r="H132" s="8" t="n"/>
+      <c r="I132" s="8" t="n"/>
       <c r="J132" s="6">
         <f>IF(H132=0, "N/A", (I132-H132)/H132)</f>
         <v/>
@@ -34286,34 +34224,34 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Sweaters</t>
+          <t>Jeans</t>
         </is>
       </c>
       <c r="B133" s="8" t="n">
-        <v>256900</v>
+        <v>1861652.3996</v>
       </c>
       <c r="C133" s="8" t="n">
-        <v>132800</v>
+        <v>1160072.0382</v>
       </c>
       <c r="D133" s="6">
         <f>IF(B133=0, "N/A", (C133-B133)/B133)</f>
         <v/>
       </c>
       <c r="E133" s="8" t="n">
-        <v>414000</v>
+        <v>664657.3393999999</v>
       </c>
       <c r="F133" s="8" t="n">
-        <v>91980</v>
+        <v>1248229.9203</v>
       </c>
       <c r="G133" s="6">
         <f>IF(E133=0, "N/A", (F133-E133)/E133)</f>
         <v/>
       </c>
       <c r="H133" s="8" t="n">
-        <v>934700</v>
+        <v>6401548.4722</v>
       </c>
       <c r="I133" s="8" t="n">
-        <v>79000</v>
+        <v>10077844.5648</v>
       </c>
       <c r="J133" s="6">
         <f>IF(H133=0, "N/A", (I133-H133)/H133)</f>
@@ -34335,25 +34273,33 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Trajes De Baño</t>
+          <t>Jogging</t>
         </is>
       </c>
       <c r="B134" s="8" t="n">
-        <v>37800</v>
+        <v>88500</v>
       </c>
       <c r="C134" s="8" t="n"/>
       <c r="D134" s="6">
         <f>IF(B134=0, "N/A", (C134-B134)/B134)</f>
         <v/>
       </c>
-      <c r="E134" s="8" t="n"/>
-      <c r="F134" s="8" t="n"/>
+      <c r="E134" s="8" t="n">
+        <v>91986.2179</v>
+      </c>
+      <c r="F134" s="8" t="n">
+        <v>99500</v>
+      </c>
       <c r="G134" s="6">
         <f>IF(E134=0, "N/A", (F134-E134)/E134)</f>
         <v/>
       </c>
-      <c r="H134" s="8" t="n"/>
-      <c r="I134" s="8" t="n"/>
+      <c r="H134" s="8" t="n">
+        <v>133440</v>
+      </c>
+      <c r="I134" s="8" t="n">
+        <v>340150.0015</v>
+      </c>
       <c r="J134" s="6">
         <f>IF(H134=0, "N/A", (I134-H134)/H134)</f>
         <v/>
@@ -34372,166 +34318,282 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="5" t="inlineStr">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="B135" s="8" t="n">
+        <v>11000</v>
+      </c>
+      <c r="C135" s="8" t="n"/>
+      <c r="D135" s="6">
+        <f>IF(B135=0, "N/A", (C135-B135)/B135)</f>
+        <v/>
+      </c>
+      <c r="E135" s="8" t="n">
+        <v>11000</v>
+      </c>
+      <c r="F135" s="8" t="n"/>
+      <c r="G135" s="6">
+        <f>IF(E135=0, "N/A", (F135-E135)/E135)</f>
+        <v/>
+      </c>
+      <c r="H135" s="8" t="n"/>
+      <c r="I135" s="8" t="n"/>
+      <c r="J135" s="6">
+        <f>IF(H135=0, "N/A", (I135-H135)/H135)</f>
+        <v/>
+      </c>
+      <c r="K135" s="8">
+        <f>B135+E135+H135</f>
+        <v/>
+      </c>
+      <c r="L135" s="8">
+        <f>C135+F135+I135</f>
+        <v/>
+      </c>
+      <c r="M135" s="6">
+        <f>IF(K135=0, "N/A", (L135-K135)/K135)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Remeras</t>
+        </is>
+      </c>
+      <c r="B136" s="8" t="n">
+        <v>639866.334</v>
+      </c>
+      <c r="C136" s="8" t="n">
+        <v>235821.1814</v>
+      </c>
+      <c r="D136" s="6">
+        <f>IF(B136=0, "N/A", (C136-B136)/B136)</f>
+        <v/>
+      </c>
+      <c r="E136" s="8" t="n">
+        <v>701041.9536</v>
+      </c>
+      <c r="F136" s="8" t="n">
+        <v>1262224.5918</v>
+      </c>
+      <c r="G136" s="6">
+        <f>IF(E136=0, "N/A", (F136-E136)/E136)</f>
+        <v/>
+      </c>
+      <c r="H136" s="8" t="n">
+        <v>3989267.1953</v>
+      </c>
+      <c r="I136" s="8" t="n">
+        <v>3595324.9972</v>
+      </c>
+      <c r="J136" s="6">
+        <f>IF(H136=0, "N/A", (I136-H136)/H136)</f>
+        <v/>
+      </c>
+      <c r="K136" s="8">
+        <f>B136+E136+H136</f>
+        <v/>
+      </c>
+      <c r="L136" s="8">
+        <f>C136+F136+I136</f>
+        <v/>
+      </c>
+      <c r="M136" s="6">
+        <f>IF(K136=0, "N/A", (L136-K136)/K136)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Sweaters</t>
+        </is>
+      </c>
+      <c r="B137" s="8" t="n">
+        <v>256900</v>
+      </c>
+      <c r="C137" s="8" t="n">
+        <v>132800</v>
+      </c>
+      <c r="D137" s="6">
+        <f>IF(B137=0, "N/A", (C137-B137)/B137)</f>
+        <v/>
+      </c>
+      <c r="E137" s="8" t="n">
+        <v>414000</v>
+      </c>
+      <c r="F137" s="8" t="n">
+        <v>91980</v>
+      </c>
+      <c r="G137" s="6">
+        <f>IF(E137=0, "N/A", (F137-E137)/E137)</f>
+        <v/>
+      </c>
+      <c r="H137" s="8" t="n">
+        <v>934700</v>
+      </c>
+      <c r="I137" s="8" t="n">
+        <v>79000</v>
+      </c>
+      <c r="J137" s="6">
+        <f>IF(H137=0, "N/A", (I137-H137)/H137)</f>
+        <v/>
+      </c>
+      <c r="K137" s="8">
+        <f>B137+E137+H137</f>
+        <v/>
+      </c>
+      <c r="L137" s="8">
+        <f>C137+F137+I137</f>
+        <v/>
+      </c>
+      <c r="M137" s="6">
+        <f>IF(K137=0, "N/A", (L137-K137)/K137)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Trajes De Baño</t>
+        </is>
+      </c>
+      <c r="B138" s="8" t="n">
+        <v>37800</v>
+      </c>
+      <c r="C138" s="8" t="n"/>
+      <c r="D138" s="6">
+        <f>IF(B138=0, "N/A", (C138-B138)/B138)</f>
+        <v/>
+      </c>
+      <c r="E138" s="8" t="n"/>
+      <c r="F138" s="8" t="n"/>
+      <c r="G138" s="6">
+        <f>IF(E138=0, "N/A", (F138-E138)/E138)</f>
+        <v/>
+      </c>
+      <c r="H138" s="8" t="n"/>
+      <c r="I138" s="8" t="n"/>
+      <c r="J138" s="6">
+        <f>IF(H138=0, "N/A", (I138-H138)/H138)</f>
+        <v/>
+      </c>
+      <c r="K138" s="8">
+        <f>B138+E138+H138</f>
+        <v/>
+      </c>
+      <c r="L138" s="8">
+        <f>C138+F138+I138</f>
+        <v/>
+      </c>
+      <c r="M138" s="6">
+        <f>IF(K138=0, "N/A", (L138-K138)/K138)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr">
         <is>
           <t>Totals</t>
         </is>
       </c>
-      <c r="B135" s="9">
-        <f>SUM($B111:$B134)</f>
-        <v/>
-      </c>
-      <c r="C135" s="9">
-        <f>SUM($C111:$C134)</f>
-        <v/>
-      </c>
-      <c r="D135" s="7">
-        <f>IF(B135=0, "N/A", (C135-B135)/B135)</f>
-        <v/>
-      </c>
-      <c r="E135" s="9">
-        <f>SUM($E111:$E134)</f>
-        <v/>
-      </c>
-      <c r="F135" s="9">
-        <f>SUM($F111:$F134)</f>
-        <v/>
-      </c>
-      <c r="G135" s="7">
-        <f>IF(E135=0, "N/A", (F135-E135)/E135)</f>
-        <v/>
-      </c>
-      <c r="H135" s="9">
-        <f>SUM($H111:$H134)</f>
-        <v/>
-      </c>
-      <c r="I135" s="9">
-        <f>SUM($I111:$I134)</f>
-        <v/>
-      </c>
-      <c r="J135" s="7">
-        <f>IF(H135=0, "N/A", (I135-H135)/H135)</f>
-        <v/>
-      </c>
-      <c r="K135" s="9">
-        <f>SUM($K111:$K134)</f>
-        <v/>
-      </c>
-      <c r="L135" s="9">
-        <f>SUM($L111:$L134)</f>
-        <v/>
-      </c>
-      <c r="M135" s="7">
-        <f>IF(K135=0, "N/A", (L135-K135)/K135)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="1" t="inlineStr">
+      <c r="B139" s="9">
+        <f>SUM($B114:$B138)</f>
+        <v/>
+      </c>
+      <c r="C139" s="9">
+        <f>SUM($C114:$C138)</f>
+        <v/>
+      </c>
+      <c r="D139" s="7">
+        <f>IF(B139=0, "N/A", (C139-B139)/B139)</f>
+        <v/>
+      </c>
+      <c r="E139" s="9">
+        <f>SUM($E114:$E138)</f>
+        <v/>
+      </c>
+      <c r="F139" s="9">
+        <f>SUM($F114:$F138)</f>
+        <v/>
+      </c>
+      <c r="G139" s="7">
+        <f>IF(E139=0, "N/A", (F139-E139)/E139)</f>
+        <v/>
+      </c>
+      <c r="H139" s="9">
+        <f>SUM($H114:$H138)</f>
+        <v/>
+      </c>
+      <c r="I139" s="9">
+        <f>SUM($I114:$I138)</f>
+        <v/>
+      </c>
+      <c r="J139" s="7">
+        <f>IF(H139=0, "N/A", (I139-H139)/H139)</f>
+        <v/>
+      </c>
+      <c r="K139" s="9">
+        <f>SUM($K114:$K138)</f>
+        <v/>
+      </c>
+      <c r="L139" s="9">
+        <f>SUM($L114:$L138)</f>
+        <v/>
+      </c>
+      <c r="M139" s="7">
+        <f>IF(K139=0, "N/A", (L139-K139)/K139)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="inlineStr">
         <is>
           <t>YoY Sales Amount Comparison - Branch Group 2</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="B139" s="1" t="inlineStr">
+    <row r="143">
+      <c r="B143" s="1" t="inlineStr">
         <is>
           <t>VIRREYES</t>
         </is>
       </c>
-      <c r="C139" s="1" t="n"/>
-      <c r="D139" s="1" t="n"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="1" t="inlineStr">
+      <c r="C143" s="1" t="n"/>
+      <c r="D143" s="1" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="inlineStr">
         <is>
           <t>Familias</t>
         </is>
       </c>
-      <c r="B140" s="1" t="n">
+      <c r="B144" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="C140" s="1" t="n">
+      <c r="C144" s="1" t="n">
         <v>2026</v>
       </c>
-      <c r="D140" s="1" t="inlineStr">
+      <c r="D144" s="1" t="inlineStr">
         <is>
           <t>%</t>
         </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>Accesorios</t>
-        </is>
-      </c>
-      <c r="B141" s="8" t="n">
-        <v>34420</v>
-      </c>
-      <c r="C141" s="8" t="n"/>
-      <c r="D141" s="6">
-        <f>IF(B141=0, "N/A", (C141-B141)/B141)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>Boxer</t>
-        </is>
-      </c>
-      <c r="B142" s="8" t="n">
-        <v>27000</v>
-      </c>
-      <c r="C142" s="8" t="n"/>
-      <c r="D142" s="6">
-        <f>IF(B142=0, "N/A", (C142-B142)/B142)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>Buzo Cuello Redondo</t>
-        </is>
-      </c>
-      <c r="B143" s="8" t="n">
-        <v>-22500</v>
-      </c>
-      <c r="C143" s="8" t="n">
-        <v>34200</v>
-      </c>
-      <c r="D143" s="6">
-        <f>IF(B143=0, "N/A", (C143-B143)/B143)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>Buzos C Capucha</t>
-        </is>
-      </c>
-      <c r="B144" s="8" t="n">
-        <v>161500</v>
-      </c>
-      <c r="C144" s="8" t="n"/>
-      <c r="D144" s="6">
-        <f>IF(B144=0, "N/A", (C144-B144)/B144)</f>
-        <v/>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Capucha Orangutan</t>
-        </is>
-      </c>
-      <c r="B145" s="8" t="n"/>
-      <c r="C145" s="8" t="n">
-        <v>184629.9998</v>
-      </c>
+          <t>Accesorios</t>
+        </is>
+      </c>
+      <c r="B145" s="8" t="n">
+        <v>34420</v>
+      </c>
+      <c r="C145" s="8" t="n"/>
       <c r="D145" s="6">
         <f>IF(B145=0, "N/A", (C145-B145)/B145)</f>
         <v/>
@@ -34540,13 +34602,13 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Redondo Orangutan</t>
-        </is>
-      </c>
-      <c r="B146" s="8" t="n"/>
-      <c r="C146" s="8" t="n">
-        <v>77800</v>
-      </c>
+          <t>Boxer</t>
+        </is>
+      </c>
+      <c r="B146" s="8" t="n">
+        <v>27000</v>
+      </c>
+      <c r="C146" s="8" t="n"/>
       <c r="D146" s="6">
         <f>IF(B146=0, "N/A", (C146-B146)/B146)</f>
         <v/>
@@ -34555,13 +34617,15 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Buzos Medio Cierre</t>
+          <t>Buzo Cuello Redondo</t>
         </is>
       </c>
       <c r="B147" s="8" t="n">
-        <v>41000</v>
-      </c>
-      <c r="C147" s="8" t="n"/>
+        <v>-22500</v>
+      </c>
+      <c r="C147" s="8" t="n">
+        <v>34200</v>
+      </c>
       <c r="D147" s="6">
         <f>IF(B147=0, "N/A", (C147-B147)/B147)</f>
         <v/>
@@ -34570,11 +34634,11 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Camisas</t>
+          <t>Buzos C Capucha</t>
         </is>
       </c>
       <c r="B148" s="8" t="n">
-        <v>97580</v>
+        <v>161500</v>
       </c>
       <c r="C148" s="8" t="n"/>
       <c r="D148" s="6">
@@ -34585,13 +34649,13 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Camperas Capucha</t>
-        </is>
-      </c>
-      <c r="B149" s="8" t="n">
-        <v>57500</v>
-      </c>
-      <c r="C149" s="8" t="n"/>
+          <t>Buzos C Capucha Orangutan</t>
+        </is>
+      </c>
+      <c r="B149" s="8" t="n"/>
+      <c r="C149" s="8" t="n">
+        <v>184629.9998</v>
+      </c>
       <c r="D149" s="6">
         <f>IF(B149=0, "N/A", (C149-B149)/B149)</f>
         <v/>
@@ -34600,11 +34664,13 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Camperas De Abrigo</t>
+          <t>Buzos C Redondo Orangutan</t>
         </is>
       </c>
       <c r="B150" s="8" t="n"/>
-      <c r="C150" s="8" t="n"/>
+      <c r="C150" s="8" t="n">
+        <v>77800</v>
+      </c>
       <c r="D150" s="6">
         <f>IF(B150=0, "N/A", (C150-B150)/B150)</f>
         <v/>
@@ -34613,13 +34679,13 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Detroit</t>
-        </is>
-      </c>
-      <c r="B151" s="8" t="n"/>
-      <c r="C151" s="8" t="n">
-        <v>31410</v>
-      </c>
+          <t>Buzos Medio Cierre</t>
+        </is>
+      </c>
+      <c r="B151" s="8" t="n">
+        <v>41000</v>
+      </c>
+      <c r="C151" s="8" t="n"/>
       <c r="D151" s="6">
         <f>IF(B151=0, "N/A", (C151-B151)/B151)</f>
         <v/>
@@ -34628,15 +34694,13 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Jeans</t>
+          <t>Camisas</t>
         </is>
       </c>
       <c r="B152" s="8" t="n">
-        <v>281290</v>
-      </c>
-      <c r="C152" s="8" t="n">
-        <v>143382</v>
-      </c>
+        <v>97580</v>
+      </c>
+      <c r="C152" s="8" t="n"/>
       <c r="D152" s="6">
         <f>IF(B152=0, "N/A", (C152-B152)/B152)</f>
         <v/>
@@ -34645,11 +34709,11 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>Jogging</t>
+          <t>Camperas Capucha</t>
         </is>
       </c>
       <c r="B153" s="8" t="n">
-        <v>44000</v>
+        <v>57500</v>
       </c>
       <c r="C153" s="8" t="n"/>
       <c r="D153" s="6">
@@ -34660,15 +34724,11 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Remeras</t>
-        </is>
-      </c>
-      <c r="B154" s="8" t="n">
-        <v>331100</v>
-      </c>
-      <c r="C154" s="8" t="n">
-        <v>50310.00019999999</v>
-      </c>
+          <t>Camperas De Abrigo</t>
+        </is>
+      </c>
+      <c r="B154" s="8" t="n"/>
+      <c r="C154" s="8" t="n"/>
       <c r="D154" s="6">
         <f>IF(B154=0, "N/A", (C154-B154)/B154)</f>
         <v/>
@@ -34677,55 +34737,119 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Sweaters</t>
-        </is>
-      </c>
-      <c r="B155" s="8" t="n">
-        <v>43000</v>
-      </c>
-      <c r="C155" s="8" t="n"/>
+          <t>Detroit</t>
+        </is>
+      </c>
+      <c r="B155" s="8" t="n"/>
+      <c r="C155" s="8" t="n">
+        <v>31410</v>
+      </c>
       <c r="D155" s="6">
         <f>IF(B155=0, "N/A", (C155-B155)/B155)</f>
         <v/>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="5" t="inlineStr">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Jeans</t>
+        </is>
+      </c>
+      <c r="B156" s="8" t="n">
+        <v>281290</v>
+      </c>
+      <c r="C156" s="8" t="n">
+        <v>143382</v>
+      </c>
+      <c r="D156" s="6">
+        <f>IF(B156=0, "N/A", (C156-B156)/B156)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Jogging</t>
+        </is>
+      </c>
+      <c r="B157" s="8" t="n">
+        <v>44000</v>
+      </c>
+      <c r="C157" s="8" t="n"/>
+      <c r="D157" s="6">
+        <f>IF(B157=0, "N/A", (C157-B157)/B157)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Remeras</t>
+        </is>
+      </c>
+      <c r="B158" s="8" t="n">
+        <v>331100</v>
+      </c>
+      <c r="C158" s="8" t="n">
+        <v>50310.00019999999</v>
+      </c>
+      <c r="D158" s="6">
+        <f>IF(B158=0, "N/A", (C158-B158)/B158)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Sweaters</t>
+        </is>
+      </c>
+      <c r="B159" s="8" t="n">
+        <v>43000</v>
+      </c>
+      <c r="C159" s="8" t="n"/>
+      <c r="D159" s="6">
+        <f>IF(B159=0, "N/A", (C159-B159)/B159)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="inlineStr">
         <is>
           <t>Totals</t>
         </is>
       </c>
-      <c r="B156" s="9">
-        <f>SUM($B141:$B155)</f>
-        <v/>
-      </c>
-      <c r="C156" s="9">
-        <f>SUM($C141:$C155)</f>
-        <v/>
-      </c>
-      <c r="D156" s="7">
-        <f>IF(B156=0, "N/A", (C156-B156)/B156)</f>
+      <c r="B160" s="9">
+        <f>SUM($B145:$B159)</f>
+        <v/>
+      </c>
+      <c r="C160" s="9">
+        <f>SUM($C145:$C159)</f>
+        <v/>
+      </c>
+      <c r="D160" s="7">
+        <f>IF(B160=0, "N/A", (C160-B160)/B160)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="A108:M108"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="H109:I109"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="K109:L109"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="A82:F82"/>
+    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="A111:M111"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A59:D59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="A29:M29"/>
-    <mergeCell ref="E109:F109"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="A138:D138"/>
+    <mergeCell ref="H112:I112"/>
+    <mergeCell ref="E112:F112"/>
+    <mergeCell ref="K112:L112"/>
+    <mergeCell ref="A30:M30"/>
+    <mergeCell ref="A142:D142"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="B143:C143"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -34872,7 +34996,7 @@
       <c r="B6" s="3" t="n"/>
       <c r="C6" s="3" t="n"/>
       <c r="D6" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="4">
@@ -34906,15 +35030,21 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Buzos</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
+          <t>Buzos C Capucha</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>227</v>
+      </c>
       <c r="D8" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" s="3" t="n"/>
+        <v>682</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>33</v>
+      </c>
       <c r="F8" s="4">
         <f>B8+C8+D8+E8</f>
         <v/>
@@ -34923,20 +35053,20 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Capucha</t>
+          <t>Buzos C Capucha Orangutan</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>206</v>
+        <v>46</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>227</v>
+        <v>64</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>684</v>
+        <v>250</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F9" s="4">
         <f>B9+C9+D9+E9</f>
@@ -34946,20 +35076,20 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Capucha Orangutan</t>
+          <t>Buzos C Redondo Orangutan</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F10" s="4">
         <f>B10+C10+D10+E10</f>
@@ -34969,21 +35099,15 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Redondo Orangutan</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>80</v>
-      </c>
+          <t>Buzos C Redondo Rustico</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
       <c r="D11" s="3" t="n">
-        <v>241</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>15</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E11" s="3" t="n"/>
       <c r="F11" s="4">
         <f>B11+C11+D11+E11</f>
         <v/>
@@ -35712,21 +35836,27 @@
           <t>Buzo C Capucha Rustico</t>
         </is>
       </c>
-      <c r="B42" s="3" t="n"/>
+      <c r="B42" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="C42" s="3" t="n"/>
       <c r="D42" s="6">
         <f>IF(B42=0, "N/A", (C42-B42)/B42)</f>
         <v/>
       </c>
-      <c r="E42" s="3" t="n"/>
+      <c r="E42" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="F42" s="3" t="n"/>
       <c r="G42" s="6">
         <f>IF(E42=0, "N/A", (F42-E42)/E42)</f>
         <v/>
       </c>
-      <c r="H42" s="3" t="n"/>
+      <c r="H42" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="I42" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J42" s="6">
         <f>IF(H42=0, "N/A", (I42-H42)/H42)</f>
@@ -35797,30 +35927,34 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Buzos</t>
+          <t>Buzos C Capucha</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C44" s="3" t="n"/>
+        <v>335</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>206</v>
+      </c>
       <c r="D44" s="6">
         <f>IF(B44=0, "N/A", (C44-B44)/B44)</f>
         <v/>
       </c>
       <c r="E44" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F44" s="3" t="n"/>
+        <v>336</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>227</v>
+      </c>
       <c r="G44" s="6">
         <f>IF(E44=0, "N/A", (F44-E44)/E44)</f>
         <v/>
       </c>
       <c r="H44" s="3" t="n">
-        <v>7</v>
+        <v>1037</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>3</v>
+        <v>682</v>
       </c>
       <c r="J44" s="6">
         <f>IF(H44=0, "N/A", (I44-H44)/H44)</f>
@@ -35842,34 +35976,28 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Capucha</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="n">
-        <v>337</v>
-      </c>
+          <t>Buzos C Capucha Orangutan</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n"/>
       <c r="C45" s="3" t="n">
-        <v>206</v>
+        <v>46</v>
       </c>
       <c r="D45" s="6">
         <f>IF(B45=0, "N/A", (C45-B45)/B45)</f>
         <v/>
       </c>
-      <c r="E45" s="3" t="n">
-        <v>337</v>
-      </c>
+      <c r="E45" s="3" t="n"/>
       <c r="F45" s="3" t="n">
-        <v>227</v>
+        <v>64</v>
       </c>
       <c r="G45" s="6">
         <f>IF(E45=0, "N/A", (F45-E45)/E45)</f>
         <v/>
       </c>
-      <c r="H45" s="3" t="n">
-        <v>1039</v>
-      </c>
+      <c r="H45" s="3" t="n"/>
       <c r="I45" s="3" t="n">
-        <v>684</v>
+        <v>250</v>
       </c>
       <c r="J45" s="6">
         <f>IF(H45=0, "N/A", (I45-H45)/H45)</f>
@@ -35891,12 +36019,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Capucha Orangutan</t>
+          <t>Buzos C Redondo Orangutan</t>
         </is>
       </c>
       <c r="B46" s="3" t="n"/>
       <c r="C46" s="3" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D46" s="6">
         <f>IF(B46=0, "N/A", (C46-B46)/B46)</f>
@@ -35904,7 +36032,7 @@
       </c>
       <c r="E46" s="3" t="n"/>
       <c r="F46" s="3" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="G46" s="6">
         <f>IF(E46=0, "N/A", (F46-E46)/E46)</f>
@@ -35912,7 +36040,7 @@
       </c>
       <c r="H46" s="3" t="n"/>
       <c r="I46" s="3" t="n">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="J46" s="6">
         <f>IF(H46=0, "N/A", (I46-H46)/H46)</f>
@@ -35934,28 +36062,30 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Redondo Orangutan</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="n"/>
-      <c r="C47" s="3" t="n">
-        <v>60</v>
-      </c>
+          <t>Buzos C Redondo Rustico</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C47" s="3" t="n"/>
       <c r="D47" s="6">
         <f>IF(B47=0, "N/A", (C47-B47)/B47)</f>
         <v/>
       </c>
-      <c r="E47" s="3" t="n"/>
-      <c r="F47" s="3" t="n">
-        <v>80</v>
-      </c>
+      <c r="E47" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" s="3" t="n"/>
       <c r="G47" s="6">
         <f>IF(E47=0, "N/A", (F47-E47)/E47)</f>
         <v/>
       </c>
-      <c r="H47" s="3" t="n"/>
+      <c r="H47" s="3" t="n">
+        <v>7</v>
+      </c>
       <c r="I47" s="3" t="n">
-        <v>241</v>
+        <v>3</v>
       </c>
       <c r="J47" s="6">
         <f>IF(H47=0, "N/A", (I47-H47)/H47)</f>
@@ -37571,7 +37701,7 @@
       <c r="B108" s="8" t="n"/>
       <c r="C108" s="8" t="n"/>
       <c r="D108" s="8" t="n">
-        <v>767812.5361</v>
+        <v>897612.5361</v>
       </c>
       <c r="E108" s="8" t="n"/>
       <c r="F108" s="9">
@@ -37605,15 +37735,21 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Buzos</t>
-        </is>
-      </c>
-      <c r="B110" s="8" t="n"/>
-      <c r="C110" s="8" t="n"/>
+          <t>Buzos C Capucha</t>
+        </is>
+      </c>
+      <c r="B110" s="8" t="n">
+        <v>11382963.9496</v>
+      </c>
+      <c r="C110" s="8" t="n">
+        <v>12656551.8553</v>
+      </c>
       <c r="D110" s="8" t="n">
-        <v>184600</v>
-      </c>
-      <c r="E110" s="8" t="n"/>
+        <v>40501341.0298</v>
+      </c>
+      <c r="E110" s="8" t="n">
+        <v>1479200.0031</v>
+      </c>
       <c r="F110" s="9">
         <f>B110+C110+D110+E110</f>
         <v/>
@@ -37622,20 +37758,20 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Capucha</t>
+          <t>Buzos C Capucha Orangutan</t>
         </is>
       </c>
       <c r="B111" s="8" t="n">
-        <v>11382963.9496</v>
+        <v>2373445.4579</v>
       </c>
       <c r="C111" s="8" t="n">
-        <v>12656551.8553</v>
+        <v>3295049.1807</v>
       </c>
       <c r="D111" s="8" t="n">
-        <v>40631141.0298</v>
+        <v>13059912.7428</v>
       </c>
       <c r="E111" s="8" t="n">
-        <v>1479200.0031</v>
+        <v>1377239.9971</v>
       </c>
       <c r="F111" s="9">
         <f>B111+C111+D111+E111</f>
@@ -37645,20 +37781,20 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Capucha Orangutan</t>
+          <t>Buzos C Redondo Orangutan</t>
         </is>
       </c>
       <c r="B112" s="8" t="n">
-        <v>2373445.4579</v>
+        <v>2369935.6397</v>
       </c>
       <c r="C112" s="8" t="n">
-        <v>3295049.1807</v>
+        <v>3153441.2994</v>
       </c>
       <c r="D112" s="8" t="n">
-        <v>13059912.7428</v>
+        <v>9557748.638800001</v>
       </c>
       <c r="E112" s="8" t="n">
-        <v>1377239.9971</v>
+        <v>550939.9978</v>
       </c>
       <c r="F112" s="9">
         <f>B112+C112+D112+E112</f>
@@ -37668,21 +37804,15 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Redondo Orangutan</t>
-        </is>
-      </c>
-      <c r="B113" s="8" t="n">
-        <v>2369935.6397</v>
-      </c>
-      <c r="C113" s="8" t="n">
-        <v>3153441.2994</v>
-      </c>
+          <t>Buzos C Redondo Rustico</t>
+        </is>
+      </c>
+      <c r="B113" s="8" t="n"/>
+      <c r="C113" s="8" t="n"/>
       <c r="D113" s="8" t="n">
-        <v>9557748.638800001</v>
-      </c>
-      <c r="E113" s="8" t="n">
-        <v>550939.9978</v>
-      </c>
+        <v>184600</v>
+      </c>
+      <c r="E113" s="8" t="n"/>
       <c r="F113" s="9">
         <f>B113+C113+D113+E113</f>
         <v/>
@@ -38413,21 +38543,27 @@
           <t>Buzo C Capucha Rustico</t>
         </is>
       </c>
-      <c r="B144" s="8" t="n"/>
+      <c r="B144" s="8" t="n">
+        <v>81317.4246</v>
+      </c>
       <c r="C144" s="8" t="n"/>
       <c r="D144" s="6">
         <f>IF(B144=0, "N/A", (C144-B144)/B144)</f>
         <v/>
       </c>
-      <c r="E144" s="8" t="n"/>
+      <c r="E144" s="8" t="n">
+        <v>47881.5866</v>
+      </c>
       <c r="F144" s="8" t="n"/>
       <c r="G144" s="6">
         <f>IF(E144=0, "N/A", (F144-E144)/E144)</f>
         <v/>
       </c>
-      <c r="H144" s="8" t="n"/>
+      <c r="H144" s="8" t="n">
+        <v>112000</v>
+      </c>
       <c r="I144" s="8" t="n">
-        <v>767812.5361</v>
+        <v>897612.5361</v>
       </c>
       <c r="J144" s="6">
         <f>IF(H144=0, "N/A", (I144-H144)/H144)</f>
@@ -38498,30 +38634,34 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Buzos</t>
+          <t>Buzos C Capucha</t>
         </is>
       </c>
       <c r="B146" s="8" t="n">
-        <v>279498</v>
-      </c>
-      <c r="C146" s="8" t="n"/>
+        <v>16454205.423</v>
+      </c>
+      <c r="C146" s="8" t="n">
+        <v>11382963.9496</v>
+      </c>
       <c r="D146" s="6">
         <f>IF(B146=0, "N/A", (C146-B146)/B146)</f>
         <v/>
       </c>
       <c r="E146" s="8" t="n">
-        <v>79899</v>
-      </c>
-      <c r="F146" s="8" t="n"/>
+        <v>16851939.7916</v>
+      </c>
+      <c r="F146" s="8" t="n">
+        <v>12656551.8553</v>
+      </c>
       <c r="G146" s="6">
         <f>IF(E146=0, "N/A", (F146-E146)/E146)</f>
         <v/>
       </c>
       <c r="H146" s="8" t="n">
-        <v>311500</v>
+        <v>56958578.2742</v>
       </c>
       <c r="I146" s="8" t="n">
-        <v>184600</v>
+        <v>40501341.0298</v>
       </c>
       <c r="J146" s="6">
         <f>IF(H146=0, "N/A", (I146-H146)/H146)</f>
@@ -38543,34 +38683,28 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Capucha</t>
-        </is>
-      </c>
-      <c r="B147" s="8" t="n">
-        <v>16535522.8476</v>
-      </c>
+          <t>Buzos C Capucha Orangutan</t>
+        </is>
+      </c>
+      <c r="B147" s="8" t="n"/>
       <c r="C147" s="8" t="n">
-        <v>11382963.9496</v>
+        <v>2373445.4579</v>
       </c>
       <c r="D147" s="6">
         <f>IF(B147=0, "N/A", (C147-B147)/B147)</f>
         <v/>
       </c>
-      <c r="E147" s="8" t="n">
-        <v>16899821.3782</v>
-      </c>
+      <c r="E147" s="8" t="n"/>
       <c r="F147" s="8" t="n">
-        <v>12656551.8553</v>
+        <v>3295049.1807</v>
       </c>
       <c r="G147" s="6">
         <f>IF(E147=0, "N/A", (F147-E147)/E147)</f>
         <v/>
       </c>
-      <c r="H147" s="8" t="n">
-        <v>57070578.2742</v>
-      </c>
+      <c r="H147" s="8" t="n"/>
       <c r="I147" s="8" t="n">
-        <v>40631141.0298</v>
+        <v>13059912.7428</v>
       </c>
       <c r="J147" s="6">
         <f>IF(H147=0, "N/A", (I147-H147)/H147)</f>
@@ -38592,12 +38726,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Capucha Orangutan</t>
+          <t>Buzos C Redondo Orangutan</t>
         </is>
       </c>
       <c r="B148" s="8" t="n"/>
       <c r="C148" s="8" t="n">
-        <v>2373445.4579</v>
+        <v>2369935.6397</v>
       </c>
       <c r="D148" s="6">
         <f>IF(B148=0, "N/A", (C148-B148)/B148)</f>
@@ -38605,7 +38739,7 @@
       </c>
       <c r="E148" s="8" t="n"/>
       <c r="F148" s="8" t="n">
-        <v>3295049.1807</v>
+        <v>3153441.2994</v>
       </c>
       <c r="G148" s="6">
         <f>IF(E148=0, "N/A", (F148-E148)/E148)</f>
@@ -38613,7 +38747,7 @@
       </c>
       <c r="H148" s="8" t="n"/>
       <c r="I148" s="8" t="n">
-        <v>13059912.7428</v>
+        <v>9557748.638800001</v>
       </c>
       <c r="J148" s="6">
         <f>IF(H148=0, "N/A", (I148-H148)/H148)</f>
@@ -38635,28 +38769,30 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Buzos C Redondo Orangutan</t>
-        </is>
-      </c>
-      <c r="B149" s="8" t="n"/>
-      <c r="C149" s="8" t="n">
-        <v>2369935.6397</v>
-      </c>
+          <t>Buzos C Redondo Rustico</t>
+        </is>
+      </c>
+      <c r="B149" s="8" t="n">
+        <v>279498</v>
+      </c>
+      <c r="C149" s="8" t="n"/>
       <c r="D149" s="6">
         <f>IF(B149=0, "N/A", (C149-B149)/B149)</f>
         <v/>
       </c>
-      <c r="E149" s="8" t="n"/>
-      <c r="F149" s="8" t="n">
-        <v>3153441.2994</v>
-      </c>
+      <c r="E149" s="8" t="n">
+        <v>79899</v>
+      </c>
+      <c r="F149" s="8" t="n"/>
       <c r="G149" s="6">
         <f>IF(E149=0, "N/A", (F149-E149)/E149)</f>
         <v/>
       </c>
-      <c r="H149" s="8" t="n"/>
+      <c r="H149" s="8" t="n">
+        <v>311500</v>
+      </c>
       <c r="I149" s="8" t="n">
-        <v>9557748.638800001</v>
+        <v>184600</v>
       </c>
       <c r="J149" s="6">
         <f>IF(H149=0, "N/A", (I149-H149)/H149)</f>
